--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="344">
   <si>
     <t>50001591 - "ZITRON COLOMBIA  ARIS MARAMTO"</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t>Apertura pedido</t>
+  </si>
+  <si>
+    <t>Carlos Pérez</t>
+  </si>
+  <si>
+    <t>cperez@zitron.com</t>
   </si>
   <si>
     <t xml:space="preserve">Buenas,
@@ -126,42 +132,45 @@
  </t>
   </si>
   <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>1217119227877897</t>
+  </si>
+  <si>
+    <t>Alcance del proyecto</t>
+  </si>
+  <si>
+    <t>1217119227877913</t>
+  </si>
+  <si>
+    <t>Definicion Tecnica de componentes principales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria Detalle,Reserva Alabes OT 4394 ,Reserva rodete  OT 4394  ,Ingenieria Basica Motor </t>
+  </si>
+  <si>
+    <t>1217117619809519</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>1217120302071407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria Basica Motor </t>
+  </si>
+  <si>
+    <t>Propuesta Motor ot 4394</t>
+  </si>
+  <si>
     <t>Baja</t>
   </si>
   <si>
-    <t>1217119227877897</t>
-  </si>
-  <si>
-    <t>Alcance del proyecto</t>
-  </si>
-  <si>
-    <t>1217119227877913</t>
-  </si>
-  <si>
-    <t>Definicion Tecnica de componentes principales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria Detalle,Reserva Alabes OT 4394 ,Reserva rodete  OT 4394  ,Ingenieria Basica Motor </t>
-  </si>
-  <si>
-    <t>1217117619809519</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>1217120302071407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria Basica Motor </t>
-  </si>
-  <si>
-    <t>Propuesta Motor ot 4394</t>
-  </si>
-  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
@@ -186,6 +195,12 @@
     <t xml:space="preserve">Reserva Alabes OT 4394 </t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
     <t>Recepcion Alabe OT 4394,Reservas</t>
   </si>
   <si>
@@ -267,6 +282,12 @@
     <t>1217119015630789</t>
   </si>
   <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
     <t>Fabricacion corte laser  ot 4394 ,Generación OC corte laser   ot 4394</t>
   </si>
   <si>
@@ -342,6 +363,12 @@
     <t>Fabricación externa   OT 4394</t>
   </si>
   <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Generacion Oc 4394,Armado  OT4394,Control de calidad   OT 4394 </t>
   </si>
   <si>
@@ -369,12 +396,24 @@
     <t xml:space="preserve">Control de calidad   OT 4394 </t>
   </si>
   <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
     <t>1217117339188567</t>
   </si>
   <si>
     <t>Motor OT 4394</t>
   </si>
   <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Generación OC Motor OT 4394,Fabricación Motor OT 4394 ,Planos motor proveedor OT 4394 </t>
   </si>
   <si>
@@ -417,6 +456,12 @@
     <t>Plano Preliminar  OT 4394</t>
   </si>
   <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
     <t>Ingenieria y diseñoo:,Plano Definitivos  OT 4394</t>
   </si>
   <si>
@@ -444,6 +489,12 @@
     <t>Check pruebas FAT  OT 4394</t>
   </si>
   <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
     <t>OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
@@ -468,6 +519,12 @@
     <t>Check pruebas FAT  OT 4394,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
+    <t>1217157927256361</t>
+  </si>
+  <si>
+    <t>OT4 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+  </si>
+  <si>
     <t>1217119120644524</t>
   </si>
   <si>
@@ -483,6 +540,12 @@
     <t>Recepcion corte laser   OT 4394</t>
   </si>
   <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
     <t>Bodega ,Control de calidad corte Laser OT 4394</t>
   </si>
   <si>
@@ -543,6 +606,12 @@
     <t>Preparacion materiales  OT 4394</t>
   </si>
   <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
     <t>OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,Caldereria</t>
   </si>
   <si>
@@ -573,6 +642,9 @@
     <t>Control de calidad Corte plasma  OT 4394,Control de calidad Mecanizado  OT 4394,Check Planos  OT 4394,Preparacion materiales  OT 4394,Control de calidad corte Laser OT 4394</t>
   </si>
   <si>
+    <t>1217157927256362</t>
+  </si>
+  <si>
     <t>1217119228070760</t>
   </si>
   <si>
@@ -600,6 +672,12 @@
     <t>Control de calidad Armado OT 4394,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
+    <t>1217157927256363</t>
+  </si>
+  <si>
+    <t>OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+  </si>
+  <si>
     <t>1217119015881793</t>
   </si>
   <si>
@@ -615,7 +693,7 @@
     <t>Recepcion Alabe OT 4394</t>
   </si>
   <si>
-    <t>Bodega:,OT  4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT  4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>Bodega:,OT  4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT  4394 -ZVN 1-9-86/2 + TOB + REJ,OT4 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1217119130136803</t>
@@ -630,7 +708,7 @@
     <t>Recepcion motor OT 4394</t>
   </si>
   <si>
-    <t>Bodega:,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>Bodega:,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1217119015882066</t>
@@ -663,6 +741,9 @@
     <t>OT 4394 -ZVN 1-9-86/2 + TOB + REJ,Revestimiento OT 4394</t>
   </si>
   <si>
+    <t>1217157927256392</t>
+  </si>
+  <si>
     <t>1217117339188562</t>
   </si>
   <si>
@@ -693,6 +774,9 @@
     <t>1217120302071383</t>
   </si>
   <si>
+    <t>1217157927256374</t>
+  </si>
+  <si>
     <t>1217119130232104</t>
   </si>
   <si>
@@ -726,6 +810,9 @@
     <t>OT 4394 -ZVN 1-9-86/2 + TOB + REJ,Montaje motor OT 4394</t>
   </si>
   <si>
+    <t>1217157927256375</t>
+  </si>
+  <si>
     <t>1217119092117870</t>
   </si>
   <si>
@@ -738,19 +825,22 @@
     <t>1217119130210198</t>
   </si>
   <si>
-    <t>Montaje Rodete OT 4394,OT1 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>Montaje Rodete OT 4394,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1217119015938558</t>
   </si>
   <si>
-    <t>Montaje Rodete OT 4394,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT2 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>Montaje Rodete OT 4394,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1217119130215406</t>
   </si>
   <si>
-    <t>OT 4394 -ZVN 1-9-86/2 + TOB + REJ,Montaje Rodete OT 4394,OT3 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT 4394 -ZVN 1-9-86/2 + TOB + REJ,Montaje Rodete OT 4394,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1217157927256376</t>
   </si>
   <si>
     <t>1217119120862836</t>
@@ -759,7 +849,7 @@
     <t>Conexión eléctrica OT 4394</t>
   </si>
   <si>
-    <t>Montaje motor OT 4394,OT1 4394 -ZVN 1-9-86/2 + TOB + REJ,OT2 4394 -ZVN 1-9-86/2 + TOB + REJ,OT3 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>Montaje motor OT 4394,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>Pruebas FAT OT 4394</t>
@@ -768,27 +858,21 @@
     <t>1217120302071384</t>
   </si>
   <si>
-    <t>OT1 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
-  </si>
-  <si>
     <t>Conexión eléctrica OT 4394,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1217120302071385</t>
   </si>
   <si>
-    <t>OT2 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
-  </si>
-  <si>
     <t>1217120302071386</t>
   </si>
   <si>
-    <t>OT3 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
-  </si>
-  <si>
     <t>Conexión eléctrica OT 4394,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
+    <t>1217157927256377</t>
+  </si>
+  <si>
     <t>1217119092223788</t>
   </si>
   <si>
@@ -807,13 +891,10 @@
     <t>1217119016025823</t>
   </si>
   <si>
-    <t>OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT1 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
-  </si>
-  <si>
     <t>1217119120969125</t>
   </si>
   <si>
-    <t>OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT3 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>1217157927256378</t>
   </si>
   <si>
     <t>1217119092247135</t>
@@ -834,6 +915,9 @@
     <t>1217119228452450</t>
   </si>
   <si>
+    <t>1217157927256379</t>
+  </si>
+  <si>
     <t>1217119092278489</t>
   </si>
   <si>
@@ -849,6 +933,12 @@
     <t>Coordinacion Entrega con Cliente OT 4394</t>
   </si>
   <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
     <t>Logistica:,Embalaje OT 4394</t>
   </si>
   <si>
@@ -867,6 +957,9 @@
     <t>1217119130369132</t>
   </si>
   <si>
+    <t>1217157927256364</t>
+  </si>
+  <si>
     <t>1217119121012650</t>
   </si>
   <si>
@@ -888,6 +981,9 @@
     <t>1217119016088934</t>
   </si>
   <si>
+    <t>1217157927256365</t>
+  </si>
+  <si>
     <t>1217119228513453</t>
   </si>
   <si>
@@ -906,6 +1002,9 @@
     <t>1217119130407136</t>
   </si>
   <si>
+    <t>1217157927256366</t>
+  </si>
+  <si>
     <t>1217119228513964</t>
   </si>
   <si>
@@ -930,6 +1029,9 @@
     <t xml:space="preserve">Gestion,Costos,Despacho OT 4394 </t>
   </si>
   <si>
+    <t>1217157927256367</t>
+  </si>
+  <si>
     <t>1217119092398083</t>
   </si>
   <si>
@@ -943,6 +1045,12 @@
   </si>
   <si>
     <t>Gestion</t>
+  </si>
+  <si>
+    <t>Nicolás</t>
+  </si>
+  <si>
+    <t>nicolas.tello@zitron.com</t>
   </si>
   <si>
     <t>OT 4394 -ZVN 1-9-86/2 + TOB + REJ,Despacho OT 4394 ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
@@ -1023,12 +1131,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1478,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U115"/>
+  <dimension ref="A1:U129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -1640,7 +1748,7 @@
         <v>46237.81343594907</v>
       </c>
       <c r="D5" s="9">
-        <v>46237.81345947916</v>
+        <v>46239.56901627315</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1649,9 +1757,11 @@
         <v>26</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="I5" s="9">
         <v>46238</v>
       </c>
@@ -1662,7 +1772,7 @@
         <v>26</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M5" s="10" t="s">
         <v>26</v>
@@ -1682,8 +1792,8 @@
       <c r="R5" s="9">
         <v>46238</v>
       </c>
-      <c r="S5" s="7" t="s">
-        <v>31</v>
+      <c r="S5" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T5" s="10">
         <v>1</v>
@@ -1694,7 +1804,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="5">
         <v>46237.57030744213</v>
@@ -1703,18 +1813,20 @@
         <v>46237.813436516204</v>
       </c>
       <c r="D6" s="5">
-        <v>46237.81345935185</v>
+        <v>46239.56901194445</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="I6" s="5">
         <v>46238</v>
       </c>
@@ -1745,8 +1857,8 @@
       <c r="R6" s="5">
         <v>46238</v>
       </c>
-      <c r="S6" s="7" t="s">
-        <v>31</v>
+      <c r="S6" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T6" s="6">
         <v>1</v>
@@ -1757,7 +1869,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B7" s="9">
         <v>46237.57031221065</v>
@@ -1766,18 +1878,20 @@
         <v>46237.81343688657</v>
       </c>
       <c r="D7" s="9">
-        <v>46237.81345934028</v>
+        <v>46239.56900780092</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="I7" s="9">
         <v>46238</v>
       </c>
@@ -1800,7 +1914,7 @@
         <v>26</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q7" s="9">
         <v>46238</v>
@@ -1808,8 +1922,8 @@
       <c r="R7" s="9">
         <v>46238</v>
       </c>
-      <c r="S7" s="7" t="s">
-        <v>31</v>
+      <c r="S7" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T7" s="10">
         <v>1</v>
@@ -1820,7 +1934,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="5">
         <v>46237.57017201389</v>
@@ -1830,7 +1944,7 @@
         <v>46237.78535715278</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>25</v>
@@ -1854,7 +1968,7 @@
         <v>26</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>26</v>
@@ -1867,25 +1981,27 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="9">
         <v>46237.77875482639</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46237.81345945602</v>
+        <v>46239.56906541667</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="I9" s="9">
         <v>46239</v>
       </c>
@@ -1902,13 +2018,13 @@
         <v>26</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q9" s="9">
         <v>46240</v>
@@ -1917,36 +2033,38 @@
         <v>46239</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T9" s="10">
         <v>0</v>
       </c>
-      <c r="U9" s="11" t="s">
-        <v>43</v>
+      <c r="U9" s="12" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46237.570322175925</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46237.81345880787</v>
+        <v>46239.56906142361</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="I10" s="5">
         <v>46239</v>
       </c>
@@ -1963,13 +2081,13 @@
         <v>26</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q10" s="5">
         <v>46241</v>
@@ -1978,18 +2096,18 @@
         <v>46239</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T10" s="6">
         <v>0</v>
       </c>
-      <c r="U10" s="11" t="s">
-        <v>43</v>
+      <c r="U10" s="12" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B11" s="9">
         <v>46237.57017664352</v>
@@ -1999,7 +2117,7 @@
         <v>46237.786044988425</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>25</v>
@@ -2023,7 +2141,7 @@
         <v>26</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>26</v>
@@ -2036,25 +2154,27 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B12" s="5">
         <v>46237.5703287963</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46237.81345888889</v>
+        <v>46239.56914443287</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I12" s="5">
         <v>46238</v>
       </c>
@@ -2071,13 +2191,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Q12" s="5">
         <v>46239</v>
@@ -2086,36 +2206,38 @@
         <v>46238</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="11" t="s">
-        <v>43</v>
+      <c r="U12" s="12" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B13" s="9">
         <v>46237.570338749996</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46237.81345929398</v>
+        <v>46239.56914050926</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I13" s="9">
         <v>46238</v>
       </c>
@@ -2132,13 +2254,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="Q13" s="9">
         <v>46239</v>
@@ -2147,18 +2269,18 @@
         <v>46238</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T13" s="10">
         <v>0</v>
       </c>
-      <c r="U13" s="11" t="s">
-        <v>43</v>
+      <c r="U13" s="12" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B14" s="5">
         <v>46237.57018362268</v>
@@ -2168,7 +2290,7 @@
         <v>46237.789262673614</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2192,7 +2314,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2205,25 +2327,27 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B15" s="9">
         <v>46237.57034929398</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46237.789326342594</v>
+        <v>46239.569350798614</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I15" s="9">
         <v>46274</v>
       </c>
@@ -2240,13 +2364,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Q15" s="9">
         <v>46275</v>
@@ -2255,36 +2379,38 @@
         <v>46274</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T15" s="10">
         <v>0</v>
       </c>
-      <c r="U15" s="12" t="s">
-        <v>61</v>
+      <c r="U15" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B16" s="5">
         <v>46237.570353981486</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46237.78932667824</v>
+        <v>46239.56934689815</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I16" s="5">
         <v>46274</v>
       </c>
@@ -2301,13 +2427,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="Q16" s="5">
         <v>46275</v>
@@ -2316,36 +2442,38 @@
         <v>46274</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T16" s="6">
         <v>0</v>
       </c>
-      <c r="U16" s="12" t="s">
-        <v>61</v>
+      <c r="U16" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B17" s="9">
         <v>46237.570357986115</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46237.79325877315</v>
+        <v>46239.5693430324</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I17" s="9">
         <v>46274</v>
       </c>
@@ -2362,13 +2490,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q17" s="9">
         <v>46275</v>
@@ -2377,36 +2505,38 @@
         <v>46274</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="12" t="s">
-        <v>61</v>
+      <c r="U17" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B18" s="5">
         <v>46237.57036226852</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46237.789327280094</v>
+        <v>46239.56933935185</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I18" s="5">
         <v>46274</v>
       </c>
@@ -2423,13 +2553,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Q18" s="5">
         <v>46275</v>
@@ -2438,36 +2568,38 @@
         <v>46274</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="12" t="s">
-        <v>61</v>
+      <c r="U18" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B19" s="9">
         <v>46237.579729386576</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46238.17280878472</v>
+        <v>46239.5693828588</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="I19" s="9">
         <v>46244</v>
       </c>
@@ -2484,13 +2616,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="Q19" s="9">
         <v>46245</v>
@@ -2498,19 +2630,19 @@
       <c r="R19" s="9">
         <v>46244</v>
       </c>
-      <c r="S19" s="11" t="s">
-        <v>73</v>
+      <c r="S19" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="12" t="s">
-        <v>61</v>
+      <c r="U19" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B20" s="5">
         <v>46237.570187731486</v>
@@ -2520,7 +2652,7 @@
         <v>46237.79138571759</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2544,7 +2676,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2557,25 +2689,27 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B21" s="9">
         <v>46237.57036725694</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46237.7914609375</v>
+        <v>46239.56948452546</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="10"/>
+        <v>83</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="I21" s="9">
         <v>46276</v>
       </c>
@@ -2592,13 +2726,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q21" s="9">
         <v>46290</v>
@@ -2607,36 +2741,38 @@
         <v>46276</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="12" t="s">
-        <v>61</v>
+      <c r="U21" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B22" s="5">
         <v>46237.57037185185</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46237.79368903935</v>
+        <v>46239.569636203705</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>83</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="I22" s="5">
         <v>46276</v>
       </c>
@@ -2653,47 +2789,49 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
-      <c r="U22" s="12" t="s">
-        <v>61</v>
+      <c r="U22" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B23" s="9">
         <v>46237.57037601851</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46237.79372090277</v>
+        <v>46239.56963283565</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="10"/>
+      <c r="H23" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="I23" s="9">
         <v>46281</v>
       </c>
@@ -2710,47 +2848,49 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
       </c>
-      <c r="U23" s="12" t="s">
-        <v>61</v>
+      <c r="U23" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46237.57038045139</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46237.79174840278</v>
+        <v>46239.569480694445</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>83</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="I24" s="5">
         <v>46276</v>
       </c>
@@ -2767,10 +2907,10 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2782,36 +2922,38 @@
         <v>46276</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="12" t="s">
-        <v>61</v>
+      <c r="U24" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B25" s="9">
         <v>46237.57038452546</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46237.79378712963</v>
+        <v>46239.56972798611</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="10"/>
+        <v>83</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="I25" s="9">
         <v>46276</v>
       </c>
@@ -2828,13 +2970,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2844,25 +2986,27 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46237.57038803241</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46237.79381800926</v>
+        <v>46239.569724050925</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="6"/>
+        <v>83</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="I26" s="5">
         <v>46281</v>
       </c>
@@ -2879,13 +3023,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2895,25 +3039,27 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B27" s="9">
         <v>46237.57039190972</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46237.79294084491</v>
+        <v>46239.56947675926</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="10"/>
+        <v>83</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="I27" s="9">
         <v>46276</v>
       </c>
@@ -2930,10 +3076,10 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -2945,36 +3091,38 @@
         <v>46276</v>
       </c>
       <c r="S27" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
-      <c r="U27" s="12" t="s">
-        <v>61</v>
+      <c r="U27" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46237.570396006944</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46237.79387472222</v>
+        <v>46239.56982333334</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6"/>
+        <v>83</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="I28" s="5">
         <v>46276</v>
       </c>
@@ -2991,13 +3139,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3007,25 +3155,27 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B29" s="9">
         <v>46237.570399432865</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46237.79390055555</v>
+        <v>46239.56981936343</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="10"/>
+        <v>83</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="I29" s="9">
         <v>46281</v>
       </c>
@@ -3042,13 +3192,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3058,25 +3208,27 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5">
         <v>46237.570402893514</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46237.796086064816</v>
+        <v>46239.57001657407</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="6"/>
+        <v>110</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="I30" s="5">
         <v>46276</v>
       </c>
@@ -3093,10 +3245,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3108,36 +3260,38 @@
         <v>46276</v>
       </c>
       <c r="S30" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="12" t="s">
-        <v>61</v>
+      <c r="U30" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B31" s="9">
         <v>46237.57040684028</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46237.79551672454</v>
+        <v>46239.56992734954</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="10"/>
+        <v>110</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>111</v>
+      </c>
       <c r="I31" s="9">
         <v>46276</v>
       </c>
@@ -3154,13 +3308,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3170,25 +3324,27 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46237.570411030094</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46237.79569489583</v>
+        <v>46239.56992358796</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="6"/>
+        <v>110</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="I32" s="5">
         <v>46289</v>
       </c>
@@ -3205,13 +3361,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3221,25 +3377,27 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B33" s="9">
         <v>46237.570414699076</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46237.7958543287</v>
+        <v>46239.57014509259</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H33" s="10"/>
+        <v>121</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>122</v>
+      </c>
       <c r="I33" s="10"/>
       <c r="J33" s="9">
         <v>46318</v>
@@ -3254,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3270,25 +3428,27 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46237.580047511576</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46237.78786859954</v>
+        <v>46239.56952222223</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="6"/>
+        <v>125</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>126</v>
+      </c>
       <c r="I34" s="5">
         <v>46246</v>
       </c>
@@ -3305,10 +3465,10 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3320,18 +3480,18 @@
         <v>46246</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
-      <c r="U34" s="12" t="s">
-        <v>61</v>
+      <c r="U34" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B35" s="9">
         <v>46237.58011546296</v>
@@ -3341,7 +3501,7 @@
         <v>46237.79403800926</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3366,13 +3526,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3382,7 +3542,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46237.580208009254</v>
@@ -3392,7 +3552,7 @@
         <v>46237.79414884259</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3417,13 +3577,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3433,7 +3593,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B37" s="9">
         <v>46237.58026069445</v>
@@ -3443,7 +3603,7 @@
         <v>46237.79419584491</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3468,13 +3628,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3484,7 +3644,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B38" s="5">
         <v>46237.570455486115</v>
@@ -3494,7 +3654,7 @@
         <v>46237.810222569446</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>25</v>
@@ -3518,7 +3678,7 @@
         <v>26</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3531,25 +3691,27 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B39" s="9">
         <v>46237.57046002315</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46237.788117557866</v>
+        <v>46239.57031715278</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="10"/>
+        <v>141</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>142</v>
+      </c>
       <c r="I39" s="9">
         <v>46244</v>
       </c>
@@ -3566,13 +3728,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="Q39" s="9">
         <v>46248</v>
@@ -3581,36 +3743,38 @@
         <v>46244</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
-      <c r="U39" s="12" t="s">
-        <v>61</v>
+      <c r="U39" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46237.57046512731</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46237.78858039352</v>
+        <v>46239.570313344906</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H40" s="6"/>
+        <v>141</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="I40" s="5">
         <v>46266</v>
       </c>
@@ -3627,13 +3791,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="5">
         <v>46272</v>
@@ -3642,36 +3806,38 @@
         <v>46266</v>
       </c>
       <c r="S40" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="12" t="s">
-        <v>61</v>
+      <c r="U40" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="B41" s="9">
         <v>46237.57046940972</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46237.789101898146</v>
+        <v>46239.57030957176</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H41" s="10"/>
+        <v>141</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>142</v>
+      </c>
       <c r="I41" s="9">
         <v>46273</v>
       </c>
@@ -3688,13 +3854,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="Q41" s="9">
         <v>46273</v>
@@ -3703,36 +3869,38 @@
         <v>46273</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
       </c>
-      <c r="U41" s="12" t="s">
-        <v>61</v>
+      <c r="U41" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46237.570483483796</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46237.8102975</v>
+        <v>46239.60363896991</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H42" s="6"/>
+        <v>152</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>153</v>
+      </c>
       <c r="I42" s="5">
         <v>46322</v>
       </c>
@@ -3749,13 +3917,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="Q42" s="5">
         <v>46322</v>
@@ -3764,36 +3932,38 @@
         <v>46322</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
       </c>
-      <c r="U42" s="12" t="s">
-        <v>61</v>
+      <c r="U42" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B43" s="9">
         <v>46237.57048821759</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46237.81015322916</v>
+        <v>46239.63445903936</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H43" s="10"/>
+        <v>152</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="I43" s="9">
         <v>46322</v>
       </c>
@@ -3810,13 +3980,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -3826,25 +3996,27 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46237.57049291667</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46237.81015832176</v>
+        <v>46239.63445802083</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H44" s="6"/>
+        <v>152</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>153</v>
+      </c>
       <c r="I44" s="5">
         <v>46322</v>
       </c>
@@ -3861,13 +4033,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -3877,25 +4049,27 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="B45" s="9">
         <v>46237.57051701389</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46237.81015348379</v>
+        <v>46239.63445679398</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H45" s="10"/>
+        <v>152</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="I45" s="9">
         <v>46322</v>
       </c>
@@ -3912,13 +4086,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -3928,27 +4102,33 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46237.57052454861</v>
+        <v>46239.60363707176</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46237.796667546296</v>
+        <v>46239.63479635416</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
+        <v>152</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I46" s="5">
+        <v>46322</v>
+      </c>
+      <c r="J46" s="5">
+        <v>46322</v>
+      </c>
       <c r="K46" s="6" t="s">
         <v>26</v>
       </c>
@@ -3956,16 +4136,16 @@
         <v>26</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -3975,31 +4155,27 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B47" s="9">
-        <v>46237.57052836806</v>
+        <v>46237.57052454861</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46237.7963675</v>
+        <v>46237.796667546296</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="H47" s="10"/>
-      <c r="I47" s="9">
-        <v>46293</v>
-      </c>
-      <c r="J47" s="9">
-        <v>46293</v>
-      </c>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
       <c r="K47" s="10" t="s">
         <v>26</v>
       </c>
@@ -4007,54 +4183,46 @@
         <v>26</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>146</v>
+        <v>26</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q47" s="9">
-        <v>46293</v>
-      </c>
-      <c r="R47" s="9">
-        <v>46293</v>
-      </c>
-      <c r="S47" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T47" s="10">
-        <v>0</v>
-      </c>
-      <c r="U47" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="10"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B48" s="5">
-        <v>46237.57053329861</v>
+        <v>46237.57052836806</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46237.796368043986</v>
+        <v>46239.57054138889</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H48" s="6"/>
+        <v>169</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>170</v>
+      </c>
       <c r="I48" s="5">
         <v>46293</v>
       </c>
@@ -4071,13 +4239,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46293</v>
@@ -4086,36 +4254,38 @@
         <v>46293</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="12" t="s">
-        <v>61</v>
+      <c r="U48" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B49" s="9">
-        <v>46237.57053827547</v>
+        <v>46237.57053329861</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46237.79636827546</v>
+        <v>46239.570537754626</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H49" s="10"/>
+        <v>169</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>170</v>
+      </c>
       <c r="I49" s="9">
         <v>46293</v>
       </c>
@@ -4132,13 +4302,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="Q49" s="9">
         <v>46293</v>
@@ -4147,41 +4317,43 @@
         <v>46293</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
       </c>
-      <c r="U49" s="12" t="s">
-        <v>61</v>
+      <c r="U49" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
-        <v>46237.57054359953</v>
+        <v>46237.57053827547</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46237.79652471065</v>
+        <v>46239.570533715276</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H50" s="6"/>
+        <v>169</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>170</v>
+      </c>
       <c r="I50" s="5">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="J50" s="5">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>26</v>
@@ -4193,51 +4365,53 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="5">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="R50" s="5">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="12" t="s">
-        <v>61</v>
+      <c r="U50" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="B51" s="9">
-        <v>46237.570548668984</v>
+        <v>46237.57054359953</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46237.796525011574</v>
+        <v>46239.570621273146</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H51" s="10"/>
+        <v>121</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>122</v>
+      </c>
       <c r="I51" s="9">
         <v>46294</v>
       </c>
@@ -4254,13 +4428,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="Q51" s="9">
         <v>46294</v>
@@ -4269,36 +4443,38 @@
         <v>46294</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
-      <c r="U51" s="12" t="s">
-        <v>61</v>
+      <c r="U51" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46237.57055390046</v>
+        <v>46237.570548668984</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46237.79652523148</v>
+        <v>46239.57061776621</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H52" s="6"/>
+        <v>121</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="I52" s="5">
         <v>46294</v>
       </c>
@@ -4315,13 +4491,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="Q52" s="5">
         <v>46294</v>
@@ -4330,38 +4506,44 @@
         <v>46294</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
-      <c r="U52" s="12" t="s">
-        <v>61</v>
+      <c r="U52" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="B53" s="9">
-        <v>46237.57055873843</v>
+        <v>46237.57055390046</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46237.79991431713</v>
+        <v>46239.57061447916</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
+        <v>121</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I53" s="9">
+        <v>46294</v>
+      </c>
+      <c r="J53" s="9">
+        <v>46294</v>
+      </c>
       <c r="K53" s="10" t="s">
         <v>26</v>
       </c>
@@ -4369,50 +4551,56 @@
         <v>26</v>
       </c>
       <c r="M53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="O53" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q53" s="9">
+        <v>46294</v>
+      </c>
+      <c r="R53" s="9">
+        <v>46294</v>
+      </c>
+      <c r="S53" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T53" s="10">
         <v>0</v>
       </c>
-      <c r="N53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="P53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
+      <c r="U53" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="B54" s="5">
-        <v>46237.570562442124</v>
+        <v>46237.57055873843</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46237.799230578705</v>
+        <v>46237.79991431713</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H54" s="6"/>
-      <c r="I54" s="5">
-        <v>46295</v>
-      </c>
-      <c r="J54" s="5">
-        <v>46297</v>
-      </c>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
       <c r="K54" s="6" t="s">
         <v>26</v>
       </c>
@@ -4420,59 +4608,51 @@
         <v>26</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>166</v>
+        <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q54" s="5">
-        <v>46297</v>
-      </c>
-      <c r="R54" s="5">
-        <v>46295</v>
-      </c>
-      <c r="S54" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T54" s="6">
-        <v>0</v>
-      </c>
-      <c r="U54" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q54" s="6"/>
+      <c r="R54" s="6"/>
+      <c r="S54" s="6"/>
+      <c r="T54" s="6"/>
+      <c r="U54" s="6"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="B55" s="9">
-        <v>46237.57056796296</v>
+        <v>46237.570562442124</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46237.79954310185</v>
+        <v>46239.608869386575</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="10"/>
+        <v>191</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>192</v>
+      </c>
       <c r="I55" s="9">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="J55" s="9">
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="K55" s="10" t="s">
         <v>26</v>
@@ -4484,51 +4664,53 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="Q55" s="9">
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="R55" s="9">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
       </c>
-      <c r="U55" s="12" t="s">
-        <v>61</v>
+      <c r="U55" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
-        <v>46237.57057246528</v>
+        <v>46237.57056796296</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46237.79953744213</v>
+        <v>46239.603713460645</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="6"/>
+        <v>191</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>192</v>
+      </c>
       <c r="I56" s="5">
         <v>46300</v>
       </c>
@@ -4545,41 +4727,53 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6"/>
-      <c r="T56" s="6"/>
-      <c r="U56" s="6"/>
+        <v>187</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>46304</v>
+      </c>
+      <c r="R56" s="5">
+        <v>46300</v>
+      </c>
+      <c r="S56" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T56" s="6">
+        <v>0</v>
+      </c>
+      <c r="U56" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B57" s="9">
-        <v>46237.570579224535</v>
+        <v>46237.57057246528</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46237.79954325232</v>
+        <v>46239.57090008102</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="10"/>
+        <v>191</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>192</v>
+      </c>
       <c r="I57" s="9">
         <v>46300</v>
       </c>
@@ -4596,13 +4790,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4612,25 +4806,27 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
-        <v>46237.570585995374</v>
+        <v>46237.570579224535</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46237.79953684028</v>
+        <v>46239.570895972225</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H58" s="6"/>
+        <v>191</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>192</v>
+      </c>
       <c r="I58" s="5">
         <v>46300</v>
       </c>
@@ -4647,13 +4843,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4663,28 +4859,32 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="B59" s="9">
-        <v>46237.57064327547</v>
+        <v>46237.570585995374</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46237.8000169213</v>
+        <v>46239.570892222226</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
+        <v>191</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I59" s="9">
+        <v>46300</v>
+      </c>
       <c r="J59" s="9">
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="K59" s="10" t="s">
         <v>26</v>
@@ -4696,56 +4896,48 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q59" s="9">
-        <v>46307</v>
-      </c>
-      <c r="R59" s="9">
-        <v>46307</v>
-      </c>
-      <c r="S59" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T59" s="10">
-        <v>0</v>
-      </c>
-      <c r="U59" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="10"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
-        <v>46237.570648796296</v>
+        <v>46239.60371085648</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46237.79972575232</v>
+        <v>46239.60969225694</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="6"/>
+        <v>191</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>192</v>
+      </c>
       <c r="I60" s="5">
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="J60" s="5">
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>26</v>
@@ -4757,13 +4949,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4773,28 +4965,28 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
-        <v>46237.57065361111</v>
+        <v>46237.57064327547</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46237.79973133102</v>
+        <v>46239.60380005787</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H61" s="10"/>
-      <c r="I61" s="9">
-        <v>46307</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I61" s="10"/>
       <c r="J61" s="9">
         <v>46307</v>
       </c>
@@ -4808,41 +5000,53 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q61" s="10"/>
-      <c r="R61" s="10"/>
-      <c r="S61" s="10"/>
-      <c r="T61" s="10"/>
-      <c r="U61" s="10"/>
+        <v>187</v>
+      </c>
+      <c r="Q61" s="9">
+        <v>46307</v>
+      </c>
+      <c r="R61" s="9">
+        <v>46307</v>
+      </c>
+      <c r="S61" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T61" s="10">
+        <v>0</v>
+      </c>
+      <c r="U61" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="B62" s="5">
-        <v>46237.57065883101</v>
+        <v>46237.570648796296</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46237.799731817126</v>
+        <v>46239.57100972222</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="6"/>
+        <v>121</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="I62" s="5">
         <v>46307</v>
       </c>
@@ -4859,13 +5063,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -4875,27 +5079,33 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="B63" s="9">
-        <v>46237.57067465278</v>
+        <v>46237.57065361111</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46237.80043872685</v>
+        <v>46239.57100552083</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
+        <v>121</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I63" s="9">
+        <v>46307</v>
+      </c>
+      <c r="J63" s="9">
+        <v>46307</v>
+      </c>
       <c r="K63" s="10" t="s">
         <v>26</v>
       </c>
@@ -4903,16 +5113,16 @@
         <v>26</v>
       </c>
       <c r="M63" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>26</v>
+        <v>205</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>26</v>
+        <v>208</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -4922,30 +5132,32 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B64" s="5">
-        <v>46237.570677881944</v>
+        <v>46237.57065883101</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46237.80154421296</v>
+        <v>46239.57100167824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
+        <v>121</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="I64" s="5">
-        <v>46240</v>
+        <v>46307</v>
       </c>
       <c r="J64" s="5">
-        <v>46241</v>
+        <v>46307</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
@@ -4957,56 +5169,46 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>50</v>
+        <v>211</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>46241</v>
-      </c>
-      <c r="R64" s="5">
-        <v>46240</v>
-      </c>
-      <c r="S64" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B65" s="9">
-        <v>46237.57068269676</v>
+        <v>46239.60379768518</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46237.80300359953</v>
+        <v>46239.6206874537</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="10"/>
-      <c r="I65" s="9">
-        <v>46240</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I65" s="10"/>
       <c r="J65" s="9">
-        <v>46241</v>
+        <v>46307</v>
       </c>
       <c r="K65" s="10" t="s">
         <v>26</v>
@@ -5018,57 +5220,43 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>53</v>
+        <v>156</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q65" s="9">
-        <v>46241</v>
-      </c>
-      <c r="R65" s="9">
-        <v>46240</v>
-      </c>
-      <c r="S65" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T65" s="10">
-        <v>0</v>
-      </c>
-      <c r="U65" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="B66" s="5">
-        <v>46237.5706884838</v>
+        <v>46237.57067465278</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46237.800272939814</v>
+        <v>46237.80043872685</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H66" s="6"/>
-      <c r="I66" s="5">
-        <v>46287</v>
-      </c>
-      <c r="J66" s="5">
-        <v>46287</v>
-      </c>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
       <c r="K66" s="6" t="s">
         <v>26</v>
       </c>
@@ -5076,56 +5264,52 @@
         <v>26</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>118</v>
+        <v>217</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q66" s="5">
-        <v>46287</v>
-      </c>
-      <c r="R66" s="5">
-        <v>46287</v>
-      </c>
-      <c r="S66" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T66" s="6">
-        <v>0</v>
-      </c>
-      <c r="U66" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
+      <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="B67" s="9">
-        <v>46237.570694027774</v>
+        <v>46237.570677881944</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46237.808683634255</v>
+        <v>46239.61681556713</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
+        <v>169</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="I67" s="9">
+        <v>46240</v>
+      </c>
+      <c r="J67" s="9">
+        <v>46241</v>
+      </c>
       <c r="K67" s="10" t="s">
         <v>26</v>
       </c>
@@ -5133,49 +5317,61 @@
         <v>26</v>
       </c>
       <c r="M67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="O67" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>46241</v>
+      </c>
+      <c r="R67" s="9">
+        <v>46240</v>
+      </c>
+      <c r="S67" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T67" s="10">
         <v>0</v>
       </c>
-      <c r="N67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O67" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q67" s="10"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="10"/>
-      <c r="T67" s="10"/>
-      <c r="U67" s="10"/>
+      <c r="U67" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B68" s="5">
-        <v>46237.57069988426</v>
+        <v>46237.57068269676</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46237.80932233796</v>
+        <v>46239.61689414352</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="6"/>
+        <v>169</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>170</v>
+      </c>
       <c r="I68" s="5">
-        <v>46308</v>
+        <v>46240</v>
       </c>
       <c r="J68" s="5">
-        <v>46314</v>
+        <v>46241</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
@@ -5187,56 +5383,58 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="Q68" s="5">
-        <v>46314</v>
+        <v>46241</v>
       </c>
       <c r="R68" s="5">
-        <v>46308</v>
+        <v>46240</v>
       </c>
       <c r="S68" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
-      <c r="U68" s="12" t="s">
-        <v>61</v>
+      <c r="U68" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B69" s="9">
-        <v>46237.57070458333</v>
+        <v>46237.5706884838</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46237.80931884259</v>
+        <v>46239.61757642361</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="10"/>
+        <v>169</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>170</v>
+      </c>
       <c r="I69" s="9">
-        <v>46308</v>
+        <v>46287</v>
       </c>
       <c r="J69" s="9">
-        <v>46314</v>
+        <v>46287</v>
       </c>
       <c r="K69" s="10" t="s">
         <v>26</v>
@@ -5248,47 +5446,53 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q69" s="10"/>
-      <c r="R69" s="10"/>
-      <c r="S69" s="10"/>
-      <c r="T69" s="10"/>
-      <c r="U69" s="10"/>
+        <v>225</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>46287</v>
+      </c>
+      <c r="R69" s="9">
+        <v>46287</v>
+      </c>
+      <c r="S69" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T69" s="10">
+        <v>0</v>
+      </c>
+      <c r="U69" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="B70" s="5">
-        <v>46237.57070806713</v>
+        <v>46237.570694027774</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46237.80931916667</v>
+        <v>46237.808683634255</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H70" s="6"/>
-      <c r="I70" s="5">
-        <v>46308</v>
-      </c>
-      <c r="J70" s="5">
-        <v>46314</v>
-      </c>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
       <c r="K70" s="6" t="s">
         <v>26</v>
       </c>
@@ -5296,16 +5500,16 @@
         <v>26</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>204</v>
+        <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5315,25 +5519,27 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="B71" s="9">
-        <v>46237.57071152778</v>
+        <v>46237.57069988426</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46237.809319293985</v>
+        <v>46239.61845846065</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>139</v>
+        <v>230</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H71" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I71" s="9">
         <v>46308</v>
       </c>
@@ -5350,46 +5556,58 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q71" s="10"/>
-      <c r="R71" s="10"/>
-      <c r="S71" s="10"/>
-      <c r="T71" s="10"/>
-      <c r="U71" s="10"/>
+        <v>227</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>46314</v>
+      </c>
+      <c r="R71" s="9">
+        <v>46308</v>
+      </c>
+      <c r="S71" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T71" s="10">
+        <v>0</v>
+      </c>
+      <c r="U71" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="B72" s="5">
-        <v>46237.5792246412</v>
+        <v>46237.57070458333</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46237.809461412035</v>
+        <v>46239.57127634259</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>211</v>
+        <v>156</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H72" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I72" s="5">
-        <v>46315</v>
+        <v>46308</v>
       </c>
       <c r="J72" s="5">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
@@ -5401,56 +5619,48 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>46315</v>
-      </c>
-      <c r="R72" s="5">
-        <v>46315</v>
-      </c>
-      <c r="S72" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="B73" s="9">
-        <v>46237.60174226852</v>
+        <v>46237.57070806713</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46237.809457129624</v>
+        <v>46239.57127222222</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I73" s="9">
-        <v>46315</v>
+        <v>46308</v>
       </c>
       <c r="J73" s="9">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="K73" s="10" t="s">
         <v>26</v>
@@ -5462,13 +5672,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>215</v>
+        <v>156</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5478,30 +5688,32 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B74" s="5">
-        <v>46237.601752048606</v>
+        <v>46237.57071152778</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46237.80946259259</v>
+        <v>46239.57126841435</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H74" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I74" s="5">
-        <v>46315</v>
+        <v>46308</v>
       </c>
       <c r="J74" s="5">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>26</v>
@@ -5513,13 +5725,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>218</v>
+        <v>156</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5529,30 +5741,32 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="B75" s="9">
-        <v>46237.60176081018</v>
+        <v>46239.61845638889</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46237.809463067126</v>
+        <v>46239.620747719906</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I75" s="9">
-        <v>46315</v>
+        <v>46308</v>
       </c>
       <c r="J75" s="9">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="K75" s="10" t="s">
         <v>26</v>
@@ -5564,13 +5778,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>218</v>
+        <v>156</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>216</v>
+        <v>26</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5580,30 +5794,32 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B76" s="5">
-        <v>46237.57076179398</v>
+        <v>46237.5792246412</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46237.809556527776</v>
+        <v>46239.6097567824</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I76" s="5">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="J76" s="5">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>26</v>
@@ -5615,56 +5831,58 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>223</v>
+        <v>26</v>
       </c>
       <c r="Q76" s="5">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="R76" s="5">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
       </c>
-      <c r="U76" s="12" t="s">
-        <v>61</v>
+      <c r="U76" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B77" s="9">
-        <v>46237.570767337966</v>
+        <v>46237.60174226852</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46237.80955099537</v>
+        <v>46239.571369108795</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I77" s="9">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="J77" s="9">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="K77" s="10" t="s">
         <v>26</v>
@@ -5676,13 +5894,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5692,30 +5910,32 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B78" s="5">
-        <v>46237.57077200232</v>
+        <v>46237.601752048606</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46237.80955126157</v>
+        <v>46239.57136590278</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I78" s="5">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="J78" s="5">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>26</v>
@@ -5727,13 +5947,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5743,30 +5963,32 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B79" s="9">
-        <v>46237.570776238426</v>
+        <v>46237.60176081018</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46237.80955672453</v>
+        <v>46239.571362627314</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I79" s="9">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="J79" s="9">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="K79" s="10" t="s">
         <v>26</v>
@@ -5778,13 +6000,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -5794,30 +6016,32 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="B80" s="5">
-        <v>46237.570741250005</v>
+        <v>46239.60975478009</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46237.80967342593</v>
+        <v>46239.62328483796</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>232</v>
+        <v>163</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I80" s="5">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="J80" s="5">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -5829,56 +6053,48 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>137</v>
+        <v>245</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46317</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46317</v>
-      </c>
-      <c r="S80" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="6"/>
+      <c r="T80" s="6"/>
+      <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B81" s="9">
-        <v>46237.57074578704</v>
+        <v>46237.57076179398</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46237.80966804398</v>
+        <v>46239.60978591435</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>139</v>
+        <v>249</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I81" s="9">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="J81" s="9">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="K81" s="10" t="s">
         <v>26</v>
@@ -5890,46 +6106,58 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q81" s="10"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="10"/>
-      <c r="T81" s="10"/>
-      <c r="U81" s="10"/>
+        <v>251</v>
+      </c>
+      <c r="Q81" s="9">
+        <v>46316</v>
+      </c>
+      <c r="R81" s="9">
+        <v>46316</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T81" s="10">
+        <v>0</v>
+      </c>
+      <c r="U81" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B82" s="5">
-        <v>46237.57074978009</v>
+        <v>46237.570767337966</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46237.80967350694</v>
+        <v>46239.61779259259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I82" s="5">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="J82" s="5">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>26</v>
@@ -5941,13 +6169,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>139</v>
+        <v>253</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -5957,30 +6185,32 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B83" s="9">
-        <v>46237.570753935186</v>
+        <v>46237.57077200232</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46237.809668333335</v>
+        <v>46239.617791365745</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I83" s="9">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="J83" s="9">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="K83" s="10" t="s">
         <v>26</v>
@@ -5992,13 +6222,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6008,30 +6238,32 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B84" s="5">
-        <v>46237.57069734954</v>
+        <v>46237.570776238426</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46237.809774629626</v>
+        <v>46239.61779011574</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>241</v>
+        <v>156</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I84" s="5">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="J84" s="5">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>26</v>
@@ -6043,56 +6275,48 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q84" s="5">
-        <v>46318</v>
-      </c>
-      <c r="R84" s="5">
-        <v>46318</v>
-      </c>
-      <c r="S84" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T84" s="6">
-        <v>0</v>
-      </c>
-      <c r="U84" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="Q84" s="6"/>
+      <c r="R84" s="6"/>
+      <c r="S84" s="6"/>
+      <c r="T84" s="6"/>
+      <c r="U84" s="6"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B85" s="9">
-        <v>46237.60193265046</v>
+        <v>46239.609783865744</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46237.80977071759</v>
+        <v>46239.617714872686</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>245</v>
+        <v>156</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I85" s="9">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="J85" s="9">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="K85" s="10" t="s">
         <v>26</v>
@@ -6104,13 +6328,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>139</v>
+        <v>257</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>246</v>
+        <v>26</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6120,30 +6344,32 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B86" s="5">
-        <v>46237.601940740744</v>
+        <v>46237.570741250005</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46237.809770844906</v>
+        <v>46239.60983028935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I86" s="5">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="J86" s="5">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>26</v>
@@ -6155,46 +6381,58 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q86" s="6"/>
-      <c r="R86" s="6"/>
-      <c r="S86" s="6"/>
-      <c r="T86" s="6"/>
-      <c r="U86" s="6"/>
+        <v>262</v>
+      </c>
+      <c r="Q86" s="5">
+        <v>46317</v>
+      </c>
+      <c r="R86" s="5">
+        <v>46317</v>
+      </c>
+      <c r="S86" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T86" s="6">
+        <v>0</v>
+      </c>
+      <c r="U86" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B87" s="9">
-        <v>46237.60194800926</v>
+        <v>46237.57074578704</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46237.8097709375</v>
+        <v>46239.57192630787</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>250</v>
+        <v>156</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I87" s="9">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="J87" s="9">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="K87" s="10" t="s">
         <v>26</v>
@@ -6206,13 +6444,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="O87" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="O87" s="10" t="s">
-        <v>139</v>
-      </c>
       <c r="P87" s="10" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6222,30 +6460,32 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B88" s="5">
-        <v>46237.570830474535</v>
+        <v>46237.57074978009</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46237.809948912036</v>
+        <v>46239.57192538194</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>243</v>
+        <v>156</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I88" s="5">
-        <v>46321</v>
+        <v>46317</v>
       </c>
       <c r="J88" s="5">
-        <v>46321</v>
+        <v>46317</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>26</v>
@@ -6257,56 +6497,48 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>201</v>
+        <v>261</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q88" s="5">
-        <v>46321</v>
-      </c>
-      <c r="R88" s="5">
-        <v>46321</v>
-      </c>
-      <c r="S88" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="6"/>
+      <c r="T88" s="6"/>
+      <c r="U88" s="6"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B89" s="9">
-        <v>46237.57083550926</v>
+        <v>46237.570753935186</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46237.80994414352</v>
+        <v>46239.57192444445</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I89" s="9">
-        <v>46321</v>
+        <v>46317</v>
       </c>
       <c r="J89" s="9">
-        <v>46321</v>
+        <v>46317</v>
       </c>
       <c r="K89" s="10" t="s">
         <v>26</v>
@@ -6318,13 +6550,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6334,30 +6566,32 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B90" s="5">
-        <v>46237.570847511575</v>
+        <v>46239.6098277662</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46237.80995037037</v>
+        <v>46239.62314922454</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I90" s="5">
-        <v>46321</v>
+        <v>46317</v>
       </c>
       <c r="J90" s="5">
-        <v>46321</v>
+        <v>46317</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>26</v>
@@ -6369,13 +6603,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>258</v>
+        <v>163</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>256</v>
+        <v>26</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6385,30 +6619,32 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B91" s="9">
-        <v>46237.570855555554</v>
+        <v>46237.57069734954</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46237.809950787036</v>
+        <v>46239.60986582176</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>139</v>
+        <v>271</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I91" s="9">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="J91" s="9">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="K91" s="10" t="s">
         <v>26</v>
@@ -6420,46 +6656,58 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q91" s="10"/>
-      <c r="R91" s="10"/>
-      <c r="S91" s="10"/>
-      <c r="T91" s="10"/>
-      <c r="U91" s="10"/>
+        <v>273</v>
+      </c>
+      <c r="Q91" s="9">
+        <v>46318</v>
+      </c>
+      <c r="R91" s="9">
+        <v>46318</v>
+      </c>
+      <c r="S91" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T91" s="10">
+        <v>0</v>
+      </c>
+      <c r="U91" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="B92" s="5">
-        <v>46237.57086628472</v>
+        <v>46237.60193265046</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46237.81056626157</v>
+        <v>46239.60990070602</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>254</v>
+        <v>156</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I92" s="5">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="J92" s="5">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>26</v>
@@ -6471,56 +6719,48 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>201</v>
+        <v>271</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>262</v>
+        <v>156</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q92" s="5">
-        <v>46323</v>
-      </c>
-      <c r="R92" s="5">
-        <v>46323</v>
-      </c>
-      <c r="S92" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T92" s="6">
-        <v>0</v>
-      </c>
-      <c r="U92" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="Q92" s="6"/>
+      <c r="R92" s="6"/>
+      <c r="S92" s="6"/>
+      <c r="T92" s="6"/>
+      <c r="U92" s="6"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="B93" s="9">
-        <v>46237.57087083333</v>
+        <v>46237.601940740744</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46237.81041377315</v>
+        <v>46239.6099468287</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I93" s="9">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="J93" s="9">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="K93" s="10" t="s">
         <v>26</v>
@@ -6532,13 +6772,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6548,30 +6788,32 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B94" s="5">
-        <v>46237.57087578704</v>
+        <v>46237.60194800926</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46237.810419375004</v>
+        <v>46239.60997769676</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I94" s="5">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="J94" s="5">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
@@ -6583,13 +6825,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6599,25 +6841,27 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B95" s="9">
-        <v>46237.57088047454</v>
+        <v>46239.609863680555</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46237.81041976852</v>
+        <v>46239.63397174768</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I95" s="9">
         <v>46323</v>
       </c>
@@ -6634,13 +6878,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>264</v>
+        <v>26</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6650,27 +6894,33 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="B96" s="5">
-        <v>46237.57088893518</v>
+        <v>46237.570830474535</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46237.81145841435</v>
+        <v>46239.61000172453</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I96" s="5">
+        <v>46321</v>
+      </c>
+      <c r="J96" s="5">
+        <v>46321</v>
+      </c>
       <c r="K96" s="6" t="s">
         <v>26</v>
       </c>
@@ -6678,49 +6928,61 @@
         <v>26</v>
       </c>
       <c r="M96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q96" s="5">
+        <v>46321</v>
+      </c>
+      <c r="R96" s="5">
+        <v>46321</v>
+      </c>
+      <c r="S96" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="N96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6"/>
-      <c r="S96" s="6"/>
-      <c r="T96" s="6"/>
-      <c r="U96" s="6"/>
+      <c r="U96" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="B97" s="9">
-        <v>46237.570892731484</v>
+        <v>46237.57083550926</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46237.81080390046</v>
+        <v>46239.572179930554</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>271</v>
+        <v>156</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I97" s="9">
-        <v>46324</v>
+        <v>46321</v>
       </c>
       <c r="J97" s="9">
-        <v>46324</v>
+        <v>46321</v>
       </c>
       <c r="K97" s="10" t="s">
         <v>26</v>
@@ -6732,56 +6994,48 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q97" s="9">
-        <v>46324</v>
-      </c>
-      <c r="R97" s="9">
-        <v>46324</v>
-      </c>
-      <c r="S97" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T97" s="10">
-        <v>0</v>
-      </c>
-      <c r="U97" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="Q97" s="10"/>
+      <c r="R97" s="10"/>
+      <c r="S97" s="10"/>
+      <c r="T97" s="10"/>
+      <c r="U97" s="10"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B98" s="5">
-        <v>46237.57089802083</v>
+        <v>46237.570847511575</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46237.81065109954</v>
+        <v>46239.57217587963</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I98" s="5">
-        <v>46324</v>
+        <v>46321</v>
       </c>
       <c r="J98" s="5">
-        <v>46324</v>
+        <v>46321</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>26</v>
@@ -6793,13 +7047,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -6809,30 +7063,32 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B99" s="9">
-        <v>46237.570901921295</v>
+        <v>46237.570855555554</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46237.81065646991</v>
+        <v>46239.57217159722</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I99" s="9">
-        <v>46324</v>
+        <v>46321</v>
       </c>
       <c r="J99" s="9">
-        <v>46324</v>
+        <v>46321</v>
       </c>
       <c r="K99" s="10" t="s">
         <v>26</v>
@@ -6844,13 +7100,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -6860,30 +7116,32 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B100" s="5">
-        <v>46237.570906064815</v>
+        <v>46239.609999629625</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46237.81065695602</v>
+        <v>46239.634635740746</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I100" s="5">
-        <v>46324</v>
+        <v>46321</v>
       </c>
       <c r="J100" s="5">
-        <v>46324</v>
+        <v>46321</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>26</v>
@@ -6895,13 +7153,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>276</v>
+        <v>163</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -6911,30 +7169,32 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B101" s="9">
-        <v>46237.57091384259</v>
+        <v>46237.57086628472</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46237.81111081019</v>
+        <v>46239.610039652776</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I101" s="9">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="J101" s="9">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="K101" s="10" t="s">
         <v>26</v>
@@ -6946,56 +7206,58 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>268</v>
+        <v>227</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="Q101" s="9">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="R101" s="9">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
       </c>
-      <c r="U101" s="12" t="s">
-        <v>61</v>
+      <c r="U101" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B102" s="5">
-        <v>46237.570918125</v>
+        <v>46237.57087083333</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46237.81090575231</v>
+        <v>46239.63361798611</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I102" s="5">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="J102" s="5">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>26</v>
@@ -7007,13 +7269,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7023,30 +7285,32 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B103" s="9">
-        <v>46237.5709225</v>
+        <v>46237.57087578704</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46237.810912326386</v>
+        <v>46239.63361701389</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I103" s="9">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="J103" s="9">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="K103" s="10" t="s">
         <v>26</v>
@@ -7058,13 +7322,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7074,30 +7338,32 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B104" s="5">
-        <v>46237.57092643519</v>
+        <v>46237.57088047454</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46237.81090603009</v>
+        <v>46239.63367186343</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I104" s="5">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="J104" s="5">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>26</v>
@@ -7109,13 +7375,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7125,30 +7391,32 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B105" s="9">
-        <v>46237.5709340162</v>
+        <v>46239.610037488426</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46237.8113753588</v>
+        <v>46239.63492467593</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>286</v>
+        <v>156</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I105" s="9">
-        <v>46328</v>
+        <v>46323</v>
       </c>
       <c r="J105" s="9">
-        <v>46328</v>
+        <v>46323</v>
       </c>
       <c r="K105" s="10" t="s">
         <v>26</v>
@@ -7160,57 +7428,43 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q105" s="9">
-        <v>46328</v>
-      </c>
-      <c r="R105" s="9">
-        <v>46328</v>
-      </c>
-      <c r="S105" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T105" s="10">
-        <v>0</v>
-      </c>
-      <c r="U105" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q105" s="10"/>
+      <c r="R105" s="10"/>
+      <c r="S105" s="10"/>
+      <c r="T105" s="10"/>
+      <c r="U105" s="10"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B106" s="5">
-        <v>46237.57093827546</v>
+        <v>46237.57088893518</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46237.81122827546</v>
+        <v>46237.81145841435</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>139</v>
+        <v>296</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H106" s="6"/>
-      <c r="I106" s="5">
-        <v>46328</v>
-      </c>
-      <c r="J106" s="5">
-        <v>46328</v>
-      </c>
+      <c r="I106" s="6"/>
+      <c r="J106" s="6"/>
       <c r="K106" s="6" t="s">
         <v>26</v>
       </c>
@@ -7218,16 +7472,16 @@
         <v>26</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>286</v>
+        <v>26</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>139</v>
+        <v>297</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>288</v>
+        <v>26</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7237,30 +7491,32 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B107" s="9">
-        <v>46237.570942280094</v>
+        <v>46237.570892731484</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46237.81123366898</v>
+        <v>46239.605107766205</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>139</v>
+        <v>299</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="10"/>
+        <v>300</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>301</v>
+      </c>
       <c r="I107" s="9">
-        <v>46328</v>
+        <v>46324</v>
       </c>
       <c r="J107" s="9">
-        <v>46328</v>
+        <v>46324</v>
       </c>
       <c r="K107" s="10" t="s">
         <v>26</v>
@@ -7272,46 +7528,58 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q107" s="10"/>
-      <c r="R107" s="10"/>
-      <c r="S107" s="10"/>
-      <c r="T107" s="10"/>
-      <c r="U107" s="10"/>
+        <v>302</v>
+      </c>
+      <c r="Q107" s="9">
+        <v>46324</v>
+      </c>
+      <c r="R107" s="9">
+        <v>46324</v>
+      </c>
+      <c r="S107" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T107" s="10">
+        <v>0</v>
+      </c>
+      <c r="U107" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="B108" s="5">
-        <v>46237.570946203705</v>
+        <v>46237.57089802083</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46237.811234085646</v>
+        <v>46239.57251351852</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>300</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>301</v>
+      </c>
       <c r="I108" s="5">
-        <v>46328</v>
+        <v>46324</v>
       </c>
       <c r="J108" s="5">
-        <v>46328</v>
+        <v>46324</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>26</v>
@@ -7323,13 +7591,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7339,30 +7607,32 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B109" s="9">
-        <v>46237.57099806713</v>
+        <v>46237.570901921295</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46237.81167829861</v>
+        <v>46239.57250958333</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>292</v>
+        <v>156</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="10"/>
+        <v>300</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>301</v>
+      </c>
       <c r="I109" s="9">
-        <v>46329</v>
+        <v>46324</v>
       </c>
       <c r="J109" s="9">
-        <v>46329</v>
+        <v>46324</v>
       </c>
       <c r="K109" s="10" t="s">
         <v>26</v>
@@ -7374,56 +7644,48 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q109" s="9">
-        <v>46329</v>
-      </c>
-      <c r="R109" s="9">
-        <v>46329</v>
-      </c>
-      <c r="S109" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T109" s="10">
-        <v>0</v>
-      </c>
-      <c r="U109" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="Q109" s="10"/>
+      <c r="R109" s="10"/>
+      <c r="S109" s="10"/>
+      <c r="T109" s="10"/>
+      <c r="U109" s="10"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B110" s="5">
-        <v>46237.571004722224</v>
+        <v>46237.570906064815</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46237.811672407406</v>
+        <v>46239.57250601852</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>300</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>301</v>
+      </c>
       <c r="I110" s="5">
-        <v>46329</v>
+        <v>46324</v>
       </c>
       <c r="J110" s="5">
-        <v>46329</v>
+        <v>46324</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>26</v>
@@ -7435,13 +7697,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7451,17 +7713,17 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B111" s="9">
-        <v>46237.57100873842</v>
+        <v>46239.605104699076</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46237.811677881946</v>
+        <v>46239.60511297453</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7470,12 +7732,8 @@
         <v>26</v>
       </c>
       <c r="H111" s="10"/>
-      <c r="I111" s="9">
-        <v>46329</v>
-      </c>
-      <c r="J111" s="9">
-        <v>46329</v>
-      </c>
+      <c r="I111" s="10"/>
+      <c r="J111" s="10"/>
       <c r="K111" s="10" t="s">
         <v>26</v>
       </c>
@@ -7486,13 +7744,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>295</v>
+        <v>26</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7502,30 +7760,32 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B112" s="5">
-        <v>46237.571012685185</v>
+        <v>46237.57091384259</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46237.81167831019</v>
+        <v>46239.60514053241</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>139</v>
+        <v>310</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I112" s="5">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="J112" s="5">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>26</v>
@@ -7537,43 +7797,59 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>139</v>
+        <v>311</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q112" s="6"/>
-      <c r="R112" s="6"/>
-      <c r="S112" s="6"/>
-      <c r="T112" s="6"/>
-      <c r="U112" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q112" s="5">
+        <v>46325</v>
+      </c>
+      <c r="R112" s="5">
+        <v>46325</v>
+      </c>
+      <c r="S112" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T112" s="6">
+        <v>0</v>
+      </c>
+      <c r="U112" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="B113" s="9">
-        <v>46237.571019675925</v>
+        <v>46237.570918125</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46237.81196827546</v>
+        <v>46239.57274636574</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>300</v>
+        <v>156</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="10"/>
-      <c r="I113" s="10"/>
-      <c r="J113" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I113" s="9">
+        <v>46325</v>
+      </c>
+      <c r="J113" s="9">
+        <v>46325</v>
+      </c>
       <c r="K113" s="10" t="s">
         <v>26</v>
       </c>
@@ -7581,16 +7857,16 @@
         <v>26</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>26</v>
+        <v>310</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>301</v>
+        <v>156</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>26</v>
+        <v>313</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7600,30 +7876,32 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B114" s="5">
-        <v>46237.571023171295</v>
+        <v>46237.5709225</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46237.81192959491</v>
+        <v>46239.57274300926</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>303</v>
+        <v>156</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I114" s="5">
-        <v>46331</v>
+        <v>46325</v>
       </c>
       <c r="J114" s="5">
-        <v>46339</v>
+        <v>46325</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>26</v>
@@ -7635,89 +7913,829 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q114" s="5">
-        <v>46339</v>
-      </c>
-      <c r="R114" s="5">
-        <v>46331</v>
-      </c>
-      <c r="S114" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T114" s="6">
-        <v>0</v>
-      </c>
-      <c r="U114" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="Q114" s="6"/>
+      <c r="R114" s="6"/>
+      <c r="S114" s="6"/>
+      <c r="T114" s="6"/>
+      <c r="U114" s="6"/>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B115" s="9">
-        <v>46237.57102857639</v>
+        <v>46237.57092643519</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46237.8119299074</v>
+        <v>46239.57273921296</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>306</v>
+        <v>156</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H115" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I115" s="9">
+        <v>46325</v>
+      </c>
+      <c r="J115" s="9">
+        <v>46325</v>
+      </c>
+      <c r="K115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N115" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="O115" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="P115" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q115" s="10"/>
+      <c r="R115" s="10"/>
+      <c r="S115" s="10"/>
+      <c r="T115" s="10"/>
+      <c r="U115" s="10"/>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B116" s="5">
+        <v>46239.60513822916</v>
+      </c>
+      <c r="C116" s="6"/>
+      <c r="D116" s="5">
+        <v>46239.605140370375</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H116" s="6"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6"/>
+      <c r="K116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N116" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="O116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="P116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q116" s="6"/>
+      <c r="R116" s="6"/>
+      <c r="S116" s="6"/>
+      <c r="T116" s="6"/>
+      <c r="U116" s="6"/>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A117" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="B117" s="9">
+        <v>46237.5709340162</v>
+      </c>
+      <c r="C117" s="10"/>
+      <c r="D117" s="9">
+        <v>46239.60517148148</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G117" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I117" s="9">
+        <v>46328</v>
+      </c>
+      <c r="J117" s="9">
+        <v>46328</v>
+      </c>
+      <c r="K117" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L117" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M117" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N117" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="O117" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="P117" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q117" s="9">
+        <v>46328</v>
+      </c>
+      <c r="R117" s="9">
+        <v>46328</v>
+      </c>
+      <c r="S117" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T117" s="10">
+        <v>0</v>
+      </c>
+      <c r="U117" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B118" s="5">
+        <v>46237.57093827546</v>
+      </c>
+      <c r="C118" s="6"/>
+      <c r="D118" s="5">
+        <v>46239.57292194445</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="I118" s="5">
+        <v>46328</v>
+      </c>
+      <c r="J118" s="5">
+        <v>46328</v>
+      </c>
+      <c r="K118" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L118" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M118" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N118" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="O118" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="P118" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q118" s="6"/>
+      <c r="R118" s="6"/>
+      <c r="S118" s="6"/>
+      <c r="T118" s="6"/>
+      <c r="U118" s="6"/>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A119" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B119" s="9">
+        <v>46237.570942280094</v>
+      </c>
+      <c r="C119" s="10"/>
+      <c r="D119" s="9">
+        <v>46239.57291828704</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F119" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I119" s="9">
+        <v>46328</v>
+      </c>
+      <c r="J119" s="9">
+        <v>46328</v>
+      </c>
+      <c r="K119" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L119" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M119" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N119" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="O119" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="P119" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q119" s="10"/>
+      <c r="R119" s="10"/>
+      <c r="S119" s="10"/>
+      <c r="T119" s="10"/>
+      <c r="U119" s="10"/>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B120" s="5">
+        <v>46237.570946203705</v>
+      </c>
+      <c r="C120" s="6"/>
+      <c r="D120" s="5">
+        <v>46239.572914687495</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G120" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="I120" s="5">
+        <v>46328</v>
+      </c>
+      <c r="J120" s="5">
+        <v>46328</v>
+      </c>
+      <c r="K120" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L120" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M120" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N120" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="O120" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="P120" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q120" s="6"/>
+      <c r="R120" s="6"/>
+      <c r="S120" s="6"/>
+      <c r="T120" s="6"/>
+      <c r="U120" s="6"/>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A121" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B121" s="9">
+        <v>46239.60516900463</v>
+      </c>
+      <c r="C121" s="10"/>
+      <c r="D121" s="9">
+        <v>46239.60517126157</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F121" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G121" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H121" s="10"/>
+      <c r="I121" s="10"/>
+      <c r="J121" s="10"/>
+      <c r="K121" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L121" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M121" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N121" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="O121" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="P121" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q121" s="10"/>
+      <c r="R121" s="10"/>
+      <c r="S121" s="10"/>
+      <c r="T121" s="10"/>
+      <c r="U121" s="10"/>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B122" s="5">
+        <v>46237.57099806713</v>
+      </c>
+      <c r="C122" s="6"/>
+      <c r="D122" s="5">
+        <v>46239.60520445602</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="I122" s="5">
+        <v>46329</v>
+      </c>
+      <c r="J122" s="5">
+        <v>46329</v>
+      </c>
+      <c r="K122" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L122" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M122" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N122" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="O122" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="P122" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q122" s="5">
+        <v>46329</v>
+      </c>
+      <c r="R122" s="5">
+        <v>46329</v>
+      </c>
+      <c r="S122" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T122" s="6">
+        <v>0</v>
+      </c>
+      <c r="U122" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A123" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="B123" s="9">
+        <v>46237.571004722224</v>
+      </c>
+      <c r="C123" s="10"/>
+      <c r="D123" s="9">
+        <v>46239.573137245374</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F123" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G123" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I123" s="9">
+        <v>46329</v>
+      </c>
+      <c r="J123" s="9">
+        <v>46329</v>
+      </c>
+      <c r="K123" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L123" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M123" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N123" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="O123" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="P123" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q123" s="10"/>
+      <c r="R123" s="10"/>
+      <c r="S123" s="10"/>
+      <c r="T123" s="10"/>
+      <c r="U123" s="10"/>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B124" s="5">
+        <v>46237.57100873842</v>
+      </c>
+      <c r="C124" s="6"/>
+      <c r="D124" s="5">
+        <v>46239.57312887731</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="I124" s="5">
+        <v>46329</v>
+      </c>
+      <c r="J124" s="5">
+        <v>46329</v>
+      </c>
+      <c r="K124" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L124" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M124" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N124" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O124" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="P124" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q124" s="6"/>
+      <c r="R124" s="6"/>
+      <c r="S124" s="6"/>
+      <c r="T124" s="6"/>
+      <c r="U124" s="6"/>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A125" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B125" s="9">
+        <v>46237.571012685185</v>
+      </c>
+      <c r="C125" s="10"/>
+      <c r="D125" s="9">
+        <v>46239.57312516204</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F125" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G125" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H125" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I125" s="9">
+        <v>46329</v>
+      </c>
+      <c r="J125" s="9">
+        <v>46329</v>
+      </c>
+      <c r="K125" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L125" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M125" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N125" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="O125" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="P125" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q125" s="10"/>
+      <c r="R125" s="10"/>
+      <c r="S125" s="10"/>
+      <c r="T125" s="10"/>
+      <c r="U125" s="10"/>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B126" s="5">
+        <v>46239.60520262731</v>
+      </c>
+      <c r="C126" s="6"/>
+      <c r="D126" s="5">
+        <v>46239.60520431713</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G126" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H126" s="6"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="6"/>
+      <c r="K126" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L126" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M126" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N126" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O126" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="P126" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q126" s="6"/>
+      <c r="R126" s="6"/>
+      <c r="S126" s="6"/>
+      <c r="T126" s="6"/>
+      <c r="U126" s="6"/>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A127" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="B127" s="9">
+        <v>46237.571019675925</v>
+      </c>
+      <c r="C127" s="10"/>
+      <c r="D127" s="9">
+        <v>46237.81196827546</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="F127" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G127" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H127" s="10"/>
+      <c r="I127" s="10"/>
+      <c r="J127" s="10"/>
+      <c r="K127" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L127" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M127" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="N127" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O127" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="P127" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q127" s="10"/>
+      <c r="R127" s="10"/>
+      <c r="S127" s="10"/>
+      <c r="T127" s="10"/>
+      <c r="U127" s="10"/>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B128" s="5">
+        <v>46237.571023171295</v>
+      </c>
+      <c r="C128" s="6"/>
+      <c r="D128" s="5">
+        <v>46239.57346402778</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G128" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="I128" s="5">
         <v>46331</v>
       </c>
-      <c r="J115" s="9">
+      <c r="J128" s="5">
         <v>46339</v>
       </c>
-      <c r="K115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N115" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="O115" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="P115" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q115" s="9">
+      <c r="K128" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L128" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M128" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N128" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="O128" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="P128" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q128" s="5">
         <v>46339</v>
       </c>
-      <c r="R115" s="9">
+      <c r="R128" s="5">
         <v>46331</v>
       </c>
-      <c r="S115" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T115" s="10">
+      <c r="S128" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T128" s="6">
         <v>0</v>
       </c>
-      <c r="U115" s="12" t="s">
-        <v>61</v>
+      <c r="U128" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A129" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B129" s="9">
+        <v>46237.57102857639</v>
+      </c>
+      <c r="C129" s="10"/>
+      <c r="D129" s="9">
+        <v>46239.573531319445</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="F129" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G129" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="H129" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I129" s="9">
+        <v>46331</v>
+      </c>
+      <c r="J129" s="9">
+        <v>46339</v>
+      </c>
+      <c r="K129" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L129" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M129" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N129" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="O129" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="P129" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q129" s="9">
+        <v>46339</v>
+      </c>
+      <c r="R129" s="9">
+        <v>46331</v>
+      </c>
+      <c r="S129" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T129" s="10">
+        <v>0</v>
+      </c>
+      <c r="U129" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46239.56906541667</v>
+        <v>46240.172489965276</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46239.56914443287</v>
+        <v>46240.19889532407</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2208,8 +2208,8 @@
       <c r="R12" s="5">
         <v>46238</v>
       </c>
-      <c r="S12" s="7" t="s">
-        <v>45</v>
+      <c r="S12" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T12" s="6">
         <v>0</v>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46239.56914050926</v>
+        <v>46240.19889122686</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>58</v>
@@ -2271,8 +2271,8 @@
       <c r="R13" s="9">
         <v>46238</v>
       </c>
-      <c r="S13" s="7" t="s">
-        <v>45</v>
+      <c r="S13" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T13" s="10">
         <v>0</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="345">
   <si>
     <t>50001591 - "ZITRON COLOMBIA  ARIS MARAMTO"</t>
   </si>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46237.79403800926</v>
+        <v>46240.824535127314</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>77</v>
@@ -3510,9 +3510,11 @@
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35" s="10"/>
+        <v>125</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="I35" s="9">
         <v>46246</v>
       </c>
@@ -3552,7 +3554,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46237.79414884259</v>
+        <v>46240.824531493054</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
@@ -3561,9 +3563,11 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H36" s="6"/>
+        <v>125</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>126</v>
+      </c>
       <c r="I36" s="5">
         <v>46255</v>
       </c>
@@ -3603,7 +3607,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46237.79419584491</v>
+        <v>46240.82452775463</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>134</v>
@@ -3612,9 +3616,11 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H37" s="10"/>
+        <v>125</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="I37" s="9">
         <v>46255</v>
       </c>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -177,58 +177,58 @@
     <t>Ingenieria Jefe de proyecto:,Plano Preliminar  OT 4394</t>
   </si>
   <si>
+    <t>1217117619809521</t>
+  </si>
+  <si>
+    <t>Reservas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva Alabes OT 4394 ,Reserva rodete  OT 4394  </t>
+  </si>
+  <si>
+    <t>1217119120448611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva Alabes OT 4394 </t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe OT 4394,Reservas</t>
+  </si>
+  <si>
+    <t>1217119227894752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva rodete  OT 4394  </t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT 4394,Reservas</t>
+  </si>
+  <si>
+    <t>1217117339188555</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta Corte laser  OT 4394</t>
+  </si>
+  <si>
+    <t>1217119120459220</t>
+  </si>
+  <si>
+    <t>Check Planos  OT 4394</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC corte laser   ot 4394</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>1217117619809521</t>
-  </si>
-  <si>
-    <t>Reservas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva Alabes OT 4394 ,Reserva rodete  OT 4394  </t>
-  </si>
-  <si>
-    <t>1217119120448611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva Alabes OT 4394 </t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe OT 4394,Reservas</t>
-  </si>
-  <si>
-    <t>1217119227894752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva rodete  OT 4394  </t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT 4394,Reservas</t>
-  </si>
-  <si>
-    <t>1217117339188555</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta Corte laser  OT 4394</t>
-  </si>
-  <si>
-    <t>1217119120459220</t>
-  </si>
-  <si>
-    <t>Check Planos  OT 4394</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC corte laser   ot 4394</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46241.17463621528</v>
+        <v>46242.172832118056</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>41</v>
@@ -2098,8 +2098,8 @@
       <c r="R10" s="5">
         <v>46239</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>48</v>
+      <c r="S10" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T10" s="6">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="9">
         <v>46237.57017664352</v>
@@ -2120,7 +2120,7 @@
         <v>46237.786044988425</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>25</v>
@@ -2144,7 +2144,7 @@
         <v>26</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>26</v>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="5">
         <v>46237.5703287963</v>
@@ -2167,16 +2167,16 @@
         <v>46240.19889532407</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I12" s="5">
         <v>46238</v>
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>37</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q12" s="5">
         <v>46239</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13" s="9">
         <v>46237.570338749996</v>
@@ -2230,16 +2230,16 @@
         <v>46240.19889122686</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I13" s="9">
         <v>46238</v>
@@ -2257,13 +2257,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O13" s="10" t="s">
         <v>37</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q13" s="9">
         <v>46239</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="5">
         <v>46237.57018362268</v>
@@ -2293,7 +2293,7 @@
         <v>46237.789262673614</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2317,7 +2317,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="9">
         <v>46237.57034929398</v>
@@ -2340,16 +2340,16 @@
         <v>46239.569350798614</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I15" s="9">
         <v>46274</v>
@@ -2367,13 +2367,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>64</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="Q15" s="9">
         <v>46275</v>
@@ -2382,7 +2382,7 @@
         <v>46274</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T15" s="10">
         <v>0</v>
@@ -2409,10 +2409,10 @@
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I16" s="5">
         <v>46274</v>
@@ -2430,10 +2430,10 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>69</v>
@@ -2445,7 +2445,7 @@
         <v>46274</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T16" s="6">
         <v>0</v>
@@ -2472,10 +2472,10 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I17" s="9">
         <v>46274</v>
@@ -2493,10 +2493,10 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P17" s="10" t="s">
         <v>72</v>
@@ -2508,7 +2508,7 @@
         <v>46274</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
@@ -2535,10 +2535,10 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I18" s="5">
         <v>46274</v>
@@ -2556,10 +2556,10 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>75</v>
@@ -2571,7 +2571,7 @@
         <v>46274</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
@@ -2619,7 +2619,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>43</v>
@@ -2744,7 +2744,7 @@
         <v>46276</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
@@ -2795,7 +2795,7 @@
         <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>88</v>
@@ -2803,7 +2803,7 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
@@ -2862,7 +2862,7 @@
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>46276</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>46276</v>
       </c>
       <c r="S27" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
@@ -3263,7 +3263,7 @@
         <v>46276</v>
       </c>
       <c r="S30" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3483,7 +3483,7 @@
         <v>46246</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3815,7 +3815,7 @@
         <v>46266</v>
       </c>
       <c r="S40" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
@@ -3836,7 +3836,7 @@
         <v>46239.57030957176</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -3878,7 +3878,7 @@
         <v>46273</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>46322</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
@@ -4263,7 +4263,7 @@
         <v>46293</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>46293</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
@@ -4389,7 +4389,7 @@
         <v>46293</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4452,7 +4452,7 @@
         <v>46294</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4515,7 +4515,7 @@
         <v>46294</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4578,7 +4578,7 @@
         <v>46294</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>46295</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4751,7 +4751,7 @@
         <v>46300</v>
       </c>
       <c r="S56" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -5024,7 +5024,7 @@
         <v>46307</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46241.17462675926</v>
+        <v>46242.17283251157</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>219</v>
@@ -5332,7 +5332,7 @@
         <v>216</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>220</v>
@@ -5343,8 +5343,8 @@
       <c r="R67" s="9">
         <v>46240</v>
       </c>
-      <c r="S67" s="7" t="s">
-        <v>48</v>
+      <c r="S67" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46241.174639108795</v>
+        <v>46242.172833854165</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>222</v>
@@ -5395,7 +5395,7 @@
         <v>216</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>220</v>
@@ -5406,8 +5406,8 @@
       <c r="R68" s="5">
         <v>46240</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>48</v>
+      <c r="S68" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -5470,7 +5470,7 @@
         <v>46287</v>
       </c>
       <c r="S69" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
@@ -5544,10 +5544,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I71" s="9">
         <v>46308</v>
@@ -5580,7 +5580,7 @@
         <v>46308</v>
       </c>
       <c r="S71" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
@@ -5607,10 +5607,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I72" s="5">
         <v>46308</v>
@@ -5660,10 +5660,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I73" s="9">
         <v>46308</v>
@@ -5713,10 +5713,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I74" s="5">
         <v>46308</v>
@@ -5766,10 +5766,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I75" s="9">
         <v>46308</v>
@@ -5819,10 +5819,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I76" s="5">
         <v>46315</v>
@@ -5855,7 +5855,7 @@
         <v>46315</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
@@ -5882,10 +5882,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I77" s="9">
         <v>46315</v>
@@ -5935,10 +5935,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I78" s="5">
         <v>46315</v>
@@ -5988,10 +5988,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I79" s="9">
         <v>46315</v>
@@ -6041,10 +6041,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I80" s="5">
         <v>46315</v>
@@ -6094,10 +6094,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I81" s="9">
         <v>46316</v>
@@ -6130,7 +6130,7 @@
         <v>46316</v>
       </c>
       <c r="S81" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
@@ -6157,10 +6157,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I82" s="5">
         <v>46316</v>
@@ -6210,10 +6210,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I83" s="9">
         <v>46316</v>
@@ -6263,10 +6263,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I84" s="5">
         <v>46316</v>
@@ -6316,10 +6316,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I85" s="9">
         <v>46316</v>
@@ -6369,10 +6369,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I86" s="5">
         <v>46317</v>
@@ -6405,7 +6405,7 @@
         <v>46317</v>
       </c>
       <c r="S86" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
@@ -6432,10 +6432,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I87" s="9">
         <v>46317</v>
@@ -6485,10 +6485,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I88" s="5">
         <v>46317</v>
@@ -6538,10 +6538,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I89" s="9">
         <v>46317</v>
@@ -6591,10 +6591,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I90" s="5">
         <v>46317</v>
@@ -6644,10 +6644,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I91" s="9">
         <v>46318</v>
@@ -6680,7 +6680,7 @@
         <v>46318</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
@@ -6707,10 +6707,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I92" s="5">
         <v>46318</v>
@@ -6760,10 +6760,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I93" s="9">
         <v>46318</v>
@@ -6813,10 +6813,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I94" s="5">
         <v>46318</v>
@@ -6866,10 +6866,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I95" s="9">
         <v>46323</v>
@@ -6919,10 +6919,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I96" s="5">
         <v>46321</v>
@@ -6955,7 +6955,7 @@
         <v>46321</v>
       </c>
       <c r="S96" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T96" s="6">
         <v>0</v>
@@ -6982,10 +6982,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I97" s="9">
         <v>46321</v>
@@ -7035,10 +7035,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I98" s="5">
         <v>46321</v>
@@ -7088,10 +7088,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I99" s="9">
         <v>46321</v>
@@ -7141,10 +7141,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I100" s="5">
         <v>46321</v>
@@ -7194,10 +7194,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I101" s="9">
         <v>46323</v>
@@ -7230,7 +7230,7 @@
         <v>46323</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
@@ -7257,10 +7257,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I102" s="5">
         <v>46323</v>
@@ -7310,10 +7310,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I103" s="9">
         <v>46323</v>
@@ -7363,10 +7363,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I104" s="5">
         <v>46323</v>
@@ -7416,10 +7416,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I105" s="9">
         <v>46323</v>
@@ -7552,7 +7552,7 @@
         <v>46324</v>
       </c>
       <c r="S107" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T107" s="10">
         <v>0</v>
@@ -7791,10 +7791,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I112" s="5">
         <v>46325</v>
@@ -7827,7 +7827,7 @@
         <v>46325</v>
       </c>
       <c r="S112" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
@@ -7854,10 +7854,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I113" s="9">
         <v>46325</v>
@@ -7907,10 +7907,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I114" s="5">
         <v>46325</v>
@@ -7960,10 +7960,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="I115" s="9">
         <v>46325</v>
@@ -8013,10 +8013,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8100,7 +8100,7 @@
         <v>46328</v>
       </c>
       <c r="S117" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T117" s="10">
         <v>0</v>
@@ -8375,7 +8375,7 @@
         <v>46329</v>
       </c>
       <c r="S122" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T122" s="6">
         <v>0</v>
@@ -8697,7 +8697,7 @@
         <v>46331</v>
       </c>
       <c r="S128" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T128" s="6">
         <v>0</v>
@@ -8760,7 +8760,7 @@
         <v>46331</v>
       </c>
       <c r="S129" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="T129" s="10">
         <v>0</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46242.172832118056</v>
+        <v>46244.740248182876</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>41</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46244.740248182876</v>
+        <v>46245.741758344906</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>41</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -3707,7 +3707,7 @@
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46241.17554848379</v>
+        <v>46248.17276726852</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>139</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="344">
   <si>
     <t>50001591 - "ZITRON COLOMBIA  ARIS MARAMTO"</t>
   </si>
@@ -460,9 +460,6 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,Plano Definitivos  OT 4394</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1217119228070413</t>
@@ -3707,7 +3704,7 @@
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46248.17276726852</v>
+        <v>46249.19352295139</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>139</v>
@@ -3751,8 +3748,8 @@
       <c r="R39" s="9">
         <v>46244</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>143</v>
+      <c r="S39" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
@@ -3763,7 +3760,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B40" s="5">
         <v>46237.57046512731</v>
@@ -3773,7 +3770,7 @@
         <v>46239.570313344906</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -3803,10 +3800,10 @@
         <v>136</v>
       </c>
       <c r="O40" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="P40" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="Q40" s="5">
         <v>46272</v>
@@ -3826,7 +3823,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B41" s="9">
         <v>46237.57046940972</v>
@@ -3866,10 +3863,10 @@
         <v>136</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q41" s="9">
         <v>46273</v>
@@ -3889,7 +3886,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46237.570483483796</v>
@@ -3899,16 +3896,16 @@
         <v>46239.60363896991</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="I42" s="5">
         <v>46322</v>
@@ -3929,7 +3926,7 @@
         <v>136</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>136</v>
@@ -3952,7 +3949,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="9">
         <v>46237.57048821759</v>
@@ -3962,16 +3959,16 @@
         <v>46239.63445903936</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="I43" s="9">
         <v>46322</v>
@@ -3989,13 +3986,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O43" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="P43" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>157</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4005,7 +4002,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46237.57049291667</v>
@@ -4015,16 +4012,16 @@
         <v>46239.63445802083</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="I44" s="5">
         <v>46322</v>
@@ -4042,13 +4039,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4058,7 +4055,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B45" s="9">
         <v>46237.57051701389</v>
@@ -4068,16 +4065,16 @@
         <v>46239.63445679398</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="I45" s="9">
         <v>46322</v>
@@ -4095,13 +4092,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4111,7 +4108,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46239.60363707176</v>
@@ -4121,16 +4118,16 @@
         <v>46239.65046148148</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="I46" s="5">
         <v>46322</v>
@@ -4148,13 +4145,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4164,7 +4161,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B47" s="9">
         <v>46237.57052454861</v>
@@ -4174,7 +4171,7 @@
         <v>46237.796667546296</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>25</v>
@@ -4198,7 +4195,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4211,7 +4208,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B48" s="5">
         <v>46237.57052836806</v>
@@ -4221,16 +4218,16 @@
         <v>46239.57054138889</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="H48" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="I48" s="5">
         <v>46293</v>
@@ -4248,13 +4245,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q48" s="5">
         <v>46293</v>
@@ -4274,7 +4271,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B49" s="9">
         <v>46237.57053329861</v>
@@ -4284,16 +4281,16 @@
         <v>46239.570537754626</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="I49" s="9">
         <v>46293</v>
@@ -4311,13 +4308,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>97</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q49" s="9">
         <v>46293</v>
@@ -4337,7 +4334,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B50" s="5">
         <v>46237.57053827547</v>
@@ -4347,16 +4344,16 @@
         <v>46239.570533715276</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="I50" s="5">
         <v>46293</v>
@@ -4374,13 +4371,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q50" s="5">
         <v>46293</v>
@@ -4400,7 +4397,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B51" s="9">
         <v>46237.57054359953</v>
@@ -4410,7 +4407,7 @@
         <v>46239.570621273146</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4437,13 +4434,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q51" s="9">
         <v>46294</v>
@@ -4463,7 +4460,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B52" s="5">
         <v>46237.570548668984</v>
@@ -4473,7 +4470,7 @@
         <v>46239.57061776621</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4500,13 +4497,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q52" s="5">
         <v>46294</v>
@@ -4526,7 +4523,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B53" s="9">
         <v>46237.57055390046</v>
@@ -4536,7 +4533,7 @@
         <v>46239.57061447916</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4563,13 +4560,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q53" s="9">
         <v>46294</v>
@@ -4589,7 +4586,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B54" s="5">
         <v>46237.57055873843</v>
@@ -4599,7 +4596,7 @@
         <v>46237.79991431713</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4623,7 +4620,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4636,7 +4633,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B55" s="9">
         <v>46237.570562442124</v>
@@ -4646,16 +4643,16 @@
         <v>46239.608869386575</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
+      <c r="H55" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I55" s="9">
         <v>46295</v>
@@ -4673,13 +4670,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q55" s="9">
         <v>46297</v>
@@ -4699,7 +4696,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B56" s="5">
         <v>46237.57056796296</v>
@@ -4709,16 +4706,16 @@
         <v>46239.603713460645</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I56" s="5">
         <v>46300</v>
@@ -4736,13 +4733,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q56" s="5">
         <v>46304</v>
@@ -4762,7 +4759,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B57" s="9">
         <v>46237.57057246528</v>
@@ -4772,16 +4769,16 @@
         <v>46239.57090008102</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I57" s="9">
         <v>46300</v>
@@ -4799,13 +4796,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O57" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4815,7 +4812,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B58" s="5">
         <v>46237.570579224535</v>
@@ -4825,16 +4822,16 @@
         <v>46239.570895972225</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I58" s="5">
         <v>46300</v>
@@ -4852,13 +4849,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4868,7 +4865,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46237.570585995374</v>
@@ -4878,16 +4875,16 @@
         <v>46239.570892222226</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I59" s="9">
         <v>46300</v>
@@ -4905,13 +4902,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4921,7 +4918,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46239.60371085648</v>
@@ -4931,16 +4928,16 @@
         <v>46239.716654814816</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I60" s="5">
         <v>46300</v>
@@ -4958,13 +4955,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4974,7 +4971,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B61" s="9">
         <v>46237.57064327547</v>
@@ -4984,7 +4981,7 @@
         <v>46239.60380005787</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5009,13 +5006,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q61" s="9">
         <v>46307</v>
@@ -5035,7 +5032,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46237.570648796296</v>
@@ -5045,7 +5042,7 @@
         <v>46239.57100972222</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5072,13 +5069,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5088,7 +5085,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B63" s="9">
         <v>46237.57065361111</v>
@@ -5098,7 +5095,7 @@
         <v>46239.57100552083</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5125,13 +5122,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5141,7 +5138,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B64" s="5">
         <v>46237.57065883101</v>
@@ -5151,7 +5148,7 @@
         <v>46239.57100167824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5178,13 +5175,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5194,7 +5191,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B65" s="9">
         <v>46239.60379768518</v>
@@ -5204,7 +5201,7 @@
         <v>46239.6206874537</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5229,13 +5226,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5245,7 +5242,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B66" s="5">
         <v>46237.57067465278</v>
@@ -5255,7 +5252,7 @@
         <v>46237.80043872685</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5279,7 +5276,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5292,7 +5289,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B67" s="9">
         <v>46237.570677881944</v>
@@ -5302,16 +5299,16 @@
         <v>46242.17283251157</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="I67" s="9">
         <v>46240</v>
@@ -5329,13 +5326,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>52</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q67" s="9">
         <v>46241</v>
@@ -5355,7 +5352,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B68" s="5">
         <v>46237.57068269676</v>
@@ -5365,16 +5362,16 @@
         <v>46242.172833854165</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="I68" s="5">
         <v>46240</v>
@@ -5392,13 +5389,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>57</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q68" s="5">
         <v>46241</v>
@@ -5418,7 +5415,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B69" s="9">
         <v>46237.5706884838</v>
@@ -5428,16 +5425,16 @@
         <v>46239.61757642361</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="I69" s="9">
         <v>46287</v>
@@ -5455,13 +5452,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>130</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q69" s="9">
         <v>46287</v>
@@ -5481,7 +5478,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B70" s="5">
         <v>46237.570694027774</v>
@@ -5491,7 +5488,7 @@
         <v>46237.808683634255</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5515,7 +5512,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5528,7 +5525,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B71" s="9">
         <v>46237.57069988426</v>
@@ -5538,7 +5535,7 @@
         <v>46239.61845846065</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5565,13 +5562,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q71" s="9">
         <v>46314</v>
@@ -5591,7 +5588,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B72" s="5">
         <v>46237.57070458333</v>
@@ -5601,7 +5598,7 @@
         <v>46239.57127634259</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5628,13 +5625,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5644,7 +5641,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B73" s="9">
         <v>46237.57070806713</v>
@@ -5654,7 +5651,7 @@
         <v>46239.57127222222</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5681,13 +5678,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5697,7 +5694,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B74" s="5">
         <v>46237.57071152778</v>
@@ -5707,7 +5704,7 @@
         <v>46239.57126841435</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5734,13 +5731,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5750,7 +5747,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B75" s="9">
         <v>46239.61845638889</v>
@@ -5760,7 +5757,7 @@
         <v>46239.620747719906</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5787,10 +5784,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -5803,7 +5800,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B76" s="5">
         <v>46237.5792246412</v>
@@ -5813,7 +5810,7 @@
         <v>46239.6097567824</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5840,10 +5837,10 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5866,7 +5863,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B77" s="9">
         <v>46237.60174226852</v>
@@ -5876,7 +5873,7 @@
         <v>46239.571369108795</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5903,13 +5900,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O77" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="P77" s="10" t="s">
         <v>242</v>
-      </c>
-      <c r="P77" s="10" t="s">
-        <v>243</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5919,7 +5916,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B78" s="5">
         <v>46237.601752048606</v>
@@ -5929,7 +5926,7 @@
         <v>46239.57136590278</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5956,13 +5953,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5972,7 +5969,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B79" s="9">
         <v>46237.60176081018</v>
@@ -5982,7 +5979,7 @@
         <v>46239.571362627314</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6009,13 +6006,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6025,7 +6022,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B80" s="5">
         <v>46239.60975478009</v>
@@ -6035,7 +6032,7 @@
         <v>46239.64953579861</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6062,13 +6059,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6078,7 +6075,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B81" s="9">
         <v>46237.57076179398</v>
@@ -6088,7 +6085,7 @@
         <v>46239.60978591435</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6115,13 +6112,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O81" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="P81" s="10" t="s">
         <v>250</v>
-      </c>
-      <c r="P81" s="10" t="s">
-        <v>251</v>
       </c>
       <c r="Q81" s="9">
         <v>46316</v>
@@ -6141,7 +6138,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B82" s="5">
         <v>46237.570767337966</v>
@@ -6151,7 +6148,7 @@
         <v>46239.61779259259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6178,13 +6175,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6194,7 +6191,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B83" s="9">
         <v>46237.57077200232</v>
@@ -6204,7 +6201,7 @@
         <v>46239.617791365745</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6231,13 +6228,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6247,7 +6244,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B84" s="5">
         <v>46237.570776238426</v>
@@ -6257,7 +6254,7 @@
         <v>46239.61779011574</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6284,13 +6281,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O84" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6300,7 +6297,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B85" s="9">
         <v>46239.609783865744</v>
@@ -6310,7 +6307,7 @@
         <v>46239.617714872686</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6337,10 +6334,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6353,7 +6350,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B86" s="5">
         <v>46237.570741250005</v>
@@ -6363,7 +6360,7 @@
         <v>46239.60983028935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6390,13 +6387,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q86" s="5">
         <v>46317</v>
@@ -6416,7 +6413,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B87" s="9">
         <v>46237.57074578704</v>
@@ -6426,7 +6423,7 @@
         <v>46239.57192630787</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6453,13 +6450,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6469,7 +6466,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B88" s="5">
         <v>46237.57074978009</v>
@@ -6479,7 +6476,7 @@
         <v>46239.57192538194</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6506,13 +6503,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6522,7 +6519,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B89" s="9">
         <v>46237.570753935186</v>
@@ -6532,7 +6529,7 @@
         <v>46239.57192444445</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6559,13 +6556,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6575,7 +6572,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B90" s="5">
         <v>46239.6098277662</v>
@@ -6585,7 +6582,7 @@
         <v>46239.62314922454</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6612,10 +6609,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6628,7 +6625,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B91" s="9">
         <v>46237.57069734954</v>
@@ -6638,7 +6635,7 @@
         <v>46239.60986582176</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6665,13 +6662,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>272</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>273</v>
       </c>
       <c r="Q91" s="9">
         <v>46318</v>
@@ -6691,7 +6688,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B92" s="5">
         <v>46237.60193265046</v>
@@ -6701,7 +6698,7 @@
         <v>46239.60990070602</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6728,13 +6725,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6744,7 +6741,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B93" s="9">
         <v>46237.601940740744</v>
@@ -6754,7 +6751,7 @@
         <v>46239.6099468287</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6781,13 +6778,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6797,7 +6794,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B94" s="5">
         <v>46237.60194800926</v>
@@ -6807,7 +6804,7 @@
         <v>46239.60997769676</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6834,13 +6831,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6850,7 +6847,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B95" s="9">
         <v>46239.609863680555</v>
@@ -6860,7 +6857,7 @@
         <v>46239.63397174768</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6887,10 +6884,10 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>26</v>
@@ -6903,7 +6900,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B96" s="5">
         <v>46237.570830474535</v>
@@ -6913,7 +6910,7 @@
         <v>46239.61000172453</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6940,13 +6937,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O96" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>282</v>
       </c>
       <c r="Q96" s="5">
         <v>46321</v>
@@ -6966,7 +6963,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B97" s="9">
         <v>46237.57083550926</v>
@@ -6976,7 +6973,7 @@
         <v>46239.572179930554</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7003,13 +7000,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7019,7 +7016,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B98" s="5">
         <v>46237.570847511575</v>
@@ -7029,7 +7026,7 @@
         <v>46239.57217587963</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7056,13 +7053,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7072,7 +7069,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B99" s="9">
         <v>46237.570855555554</v>
@@ -7082,7 +7079,7 @@
         <v>46239.57217159722</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7109,13 +7106,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7125,7 +7122,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B100" s="5">
         <v>46239.609999629625</v>
@@ -7135,7 +7132,7 @@
         <v>46239.634635740746</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7162,13 +7159,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7178,7 +7175,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B101" s="9">
         <v>46237.57086628472</v>
@@ -7188,7 +7185,7 @@
         <v>46239.610039652776</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7215,10 +7212,10 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>26</v>
@@ -7241,7 +7238,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B102" s="5">
         <v>46237.57087083333</v>
@@ -7251,7 +7248,7 @@
         <v>46239.63361798611</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7278,13 +7275,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7294,7 +7291,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B103" s="9">
         <v>46237.57087578704</v>
@@ -7304,7 +7301,7 @@
         <v>46239.63361701389</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7331,13 +7328,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7347,7 +7344,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B104" s="5">
         <v>46237.57088047454</v>
@@ -7357,7 +7354,7 @@
         <v>46239.63367186343</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7384,13 +7381,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7400,7 +7397,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B105" s="9">
         <v>46239.610037488426</v>
@@ -7410,7 +7407,7 @@
         <v>46239.65005603009</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7437,13 +7434,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7453,7 +7450,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B106" s="5">
         <v>46237.57088893518</v>
@@ -7463,7 +7460,7 @@
         <v>46237.81145841435</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>25</v>
@@ -7487,7 +7484,7 @@
         <v>26</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>26</v>
@@ -7500,7 +7497,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B107" s="9">
         <v>46237.570892731484</v>
@@ -7510,16 +7507,16 @@
         <v>46239.605107766205</v>
       </c>
       <c r="E107" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G107" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="F107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G107" s="10" t="s">
+      <c r="H107" s="10" t="s">
         <v>300</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>301</v>
       </c>
       <c r="I107" s="9">
         <v>46324</v>
@@ -7537,13 +7534,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q107" s="9">
         <v>46324</v>
@@ -7563,7 +7560,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B108" s="5">
         <v>46237.57089802083</v>
@@ -7573,16 +7570,16 @@
         <v>46239.57251351852</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>300</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>301</v>
       </c>
       <c r="I108" s="5">
         <v>46324</v>
@@ -7600,13 +7597,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7616,7 +7613,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B109" s="9">
         <v>46237.570901921295</v>
@@ -7626,16 +7623,16 @@
         <v>46239.57250958333</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>300</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>301</v>
       </c>
       <c r="I109" s="9">
         <v>46324</v>
@@ -7653,13 +7650,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7669,7 +7666,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B110" s="5">
         <v>46237.570906064815</v>
@@ -7679,16 +7676,16 @@
         <v>46239.57250601852</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>300</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>301</v>
       </c>
       <c r="I110" s="5">
         <v>46324</v>
@@ -7706,13 +7703,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7722,7 +7719,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B111" s="9">
         <v>46239.605104699076</v>
@@ -7732,16 +7729,16 @@
         <v>46239.65079266204</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>300</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>301</v>
       </c>
       <c r="I111" s="9">
         <v>46324</v>
@@ -7759,13 +7756,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7775,7 +7772,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B112" s="5">
         <v>46237.57091384259</v>
@@ -7785,7 +7782,7 @@
         <v>46239.60514053241</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7812,10 +7809,10 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>26</v>
@@ -7838,7 +7835,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B113" s="9">
         <v>46237.570918125</v>
@@ -7848,7 +7845,7 @@
         <v>46239.57274636574</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -7875,13 +7872,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7891,7 +7888,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B114" s="5">
         <v>46237.5709225</v>
@@ -7901,7 +7898,7 @@
         <v>46239.57274300926</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7928,13 +7925,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -7944,7 +7941,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B115" s="9">
         <v>46237.57092643519</v>
@@ -7954,7 +7951,7 @@
         <v>46239.57273921296</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -7981,13 +7978,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -7997,7 +7994,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B116" s="5">
         <v>46239.60513822916</v>
@@ -8007,7 +8004,7 @@
         <v>46239.65121751158</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8032,13 +8029,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8048,7 +8045,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B117" s="9">
         <v>46237.5709340162</v>
@@ -8058,16 +8055,16 @@
         <v>46239.60517148148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I117" s="9">
         <v>46328</v>
@@ -8085,13 +8082,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q117" s="9">
         <v>46328</v>
@@ -8111,7 +8108,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B118" s="5">
         <v>46237.57093827546</v>
@@ -8121,16 +8118,16 @@
         <v>46239.57292194445</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I118" s="5">
         <v>46328</v>
@@ -8148,13 +8145,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8164,7 +8161,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B119" s="9">
         <v>46237.570942280094</v>
@@ -8174,16 +8171,16 @@
         <v>46239.57291828704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H119" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I119" s="9">
         <v>46328</v>
@@ -8201,13 +8198,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8217,7 +8214,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B120" s="5">
         <v>46237.570946203705</v>
@@ -8227,16 +8224,16 @@
         <v>46239.572914687495</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I120" s="5">
         <v>46328</v>
@@ -8254,13 +8251,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8270,7 +8267,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B121" s="9">
         <v>46239.60516900463</v>
@@ -8280,16 +8277,16 @@
         <v>46239.65163626157</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I121" s="9">
         <v>46328</v>
@@ -8307,13 +8304,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8323,7 +8320,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B122" s="5">
         <v>46237.57099806713</v>
@@ -8333,16 +8330,16 @@
         <v>46239.60520445602</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I122" s="5">
         <v>46329</v>
@@ -8360,13 +8357,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q122" s="5">
         <v>46329</v>
@@ -8386,7 +8383,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B123" s="9">
         <v>46237.571004722224</v>
@@ -8396,16 +8393,16 @@
         <v>46239.573137245374</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H123" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I123" s="9">
         <v>46329</v>
@@ -8423,13 +8420,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8439,7 +8436,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B124" s="5">
         <v>46237.57100873842</v>
@@ -8449,16 +8446,16 @@
         <v>46239.57312887731</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I124" s="5">
         <v>46329</v>
@@ -8476,13 +8473,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8492,7 +8489,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B125" s="9">
         <v>46237.571012685185</v>
@@ -8502,16 +8499,16 @@
         <v>46239.57312516204</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I125" s="9">
         <v>46329</v>
@@ -8529,13 +8526,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8545,7 +8542,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B126" s="5">
         <v>46239.60520262731</v>
@@ -8555,16 +8552,16 @@
         <v>46239.65181268519</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I126" s="5">
         <v>46329</v>
@@ -8582,10 +8579,10 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -8598,7 +8595,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B127" s="9">
         <v>46237.571019675925</v>
@@ -8608,7 +8605,7 @@
         <v>46237.81196827546</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>25</v>
@@ -8632,7 +8629,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>26</v>
@@ -8645,7 +8642,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B128" s="5">
         <v>46237.571023171295</v>
@@ -8655,16 +8652,16 @@
         <v>46239.57346402778</v>
       </c>
       <c r="E128" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G128" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="F128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G128" s="6" t="s">
+      <c r="H128" s="6" t="s">
         <v>339</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>340</v>
       </c>
       <c r="I128" s="5">
         <v>46331</v>
@@ -8682,13 +8679,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q128" s="5">
         <v>46339</v>
@@ -8708,7 +8705,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B129" s="9">
         <v>46237.57102857639</v>
@@ -8718,16 +8715,16 @@
         <v>46239.573531319445</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>339</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>340</v>
       </c>
       <c r="I129" s="9">
         <v>46331</v>
@@ -8745,13 +8742,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q129" s="9">
         <v>46339</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -3667,7 +3667,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46237.810222569446</v>
+        <v>46252.60439458334</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>136</v>
@@ -3712,9 +3712,11 @@
       <c r="B39" s="9">
         <v>46237.57046002315</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46252.60438921297</v>
+      </c>
       <c r="D39" s="9">
-        <v>46252.553263333335</v>
+        <v>46252.60497945602</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>139</v>
@@ -3762,10 +3764,10 @@
         <v>33</v>
       </c>
       <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="12" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3777,7 +3779,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46251.97059328704</v>
+        <v>46252.604395</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>144</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -3508,7 +3508,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46240.824535127314</v>
+        <v>46254.16999688657</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>77</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -159,46 +159,46 @@
     <t>Ingenieria Detalle</t>
   </si>
   <si>
+    <t>1217120302071407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria Basica Motor </t>
+  </si>
+  <si>
+    <t>Propuesta Motor ot 4394</t>
+  </si>
+  <si>
+    <t>1217119129757861</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Plano Preliminar  OT 4394</t>
+  </si>
+  <si>
+    <t>1217117619809521</t>
+  </si>
+  <si>
+    <t>Reservas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva Alabes OT 4394 ,Reserva rodete  OT 4394  </t>
+  </si>
+  <si>
+    <t>1217119120448611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva Alabes OT 4394 </t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe OT 4394,Reservas</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1217120302071407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria Basica Motor </t>
-  </si>
-  <si>
-    <t>Propuesta Motor ot 4394</t>
-  </si>
-  <si>
-    <t>1217119129757861</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Plano Preliminar  OT 4394</t>
-  </si>
-  <si>
-    <t>1217117619809521</t>
-  </si>
-  <si>
-    <t>Reservas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva Alabes OT 4394 ,Reserva rodete  OT 4394  </t>
-  </si>
-  <si>
-    <t>1217119120448611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva Alabes OT 4394 </t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe OT 4394,Reservas</t>
   </si>
   <si>
     <t>1217119227894752</t>
@@ -1945,9 +1945,11 @@
       <c r="B8" s="5">
         <v>46237.57017201389</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="5">
+        <v>46255.6631494676</v>
+      </c>
       <c r="D8" s="5">
-        <v>46252.553109479166</v>
+        <v>46255.663162129626</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1982,24 +1984,28 @@
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="12" t="s">
-        <v>42</v>
+      <c r="T8" s="6">
+        <v>1</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="9">
         <v>46237.77875482639</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="9">
+        <v>46255.663131863424</v>
+      </c>
       <c r="D9" s="9">
-        <v>46241.205332928235</v>
+        <v>46255.66314921297</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>26</v>
@@ -2032,7 +2038,7 @@
         <v>37</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q9" s="9">
         <v>46240</v>
@@ -2044,15 +2050,15 @@
         <v>33</v>
       </c>
       <c r="T9" s="10">
-        <v>0</v>
-      </c>
-      <c r="U9" s="12" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="5">
         <v>46237.570322175925</v>
@@ -2097,7 +2103,7 @@
         <v>37</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q10" s="5">
         <v>46241</v>
@@ -2117,7 +2123,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="9">
         <v>46237.57017664352</v>
@@ -2127,7 +2133,7 @@
         <v>46237.786044988425</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>25</v>
@@ -2151,7 +2157,7 @@
         <v>26</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>26</v>
@@ -2164,7 +2170,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="5">
         <v>46237.5703287963</v>
@@ -2174,16 +2180,16 @@
         <v>46240.19889532407</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I12" s="5">
         <v>46238</v>
@@ -2201,13 +2207,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>37</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q12" s="5">
         <v>46239</v>
@@ -2222,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="U12" s="12" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -2243,10 +2249,10 @@
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I13" s="9">
         <v>46238</v>
@@ -2264,7 +2270,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O13" s="10" t="s">
         <v>37</v>
@@ -2285,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="12" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2353,10 +2359,10 @@
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I15" s="9">
         <v>46274</v>
@@ -2416,10 +2422,10 @@
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I16" s="5">
         <v>46274</v>
@@ -2479,10 +2485,10 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I17" s="9">
         <v>46274</v>
@@ -2542,10 +2548,10 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I18" s="5">
         <v>46274</v>
@@ -2594,12 +2600,14 @@
       <c r="B19" s="9">
         <v>46237.579729386576</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9">
+        <v>46255.66323561342</v>
+      </c>
       <c r="D19" s="9">
-        <v>46246.200580046294</v>
+        <v>46255.663251018515</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2629,7 +2637,7 @@
         <v>60</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>77</v>
@@ -2644,10 +2652,10 @@
         <v>33</v>
       </c>
       <c r="T19" s="10">
-        <v>0</v>
-      </c>
-      <c r="U19" s="11" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -3443,9 +3451,11 @@
       <c r="B34" s="5">
         <v>46237.580047511576</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46255.66337146991</v>
+      </c>
       <c r="D34" s="5">
-        <v>46239.56952222223</v>
+        <v>46255.66338287037</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>123</v>
@@ -3493,10 +3503,10 @@
         <v>65</v>
       </c>
       <c r="T34" s="6">
-        <v>0</v>
-      </c>
-      <c r="U34" s="11" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U34" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3506,9 +3516,11 @@
       <c r="B35" s="9">
         <v>46237.58011546296</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="9">
+        <v>46255.663279155095</v>
+      </c>
       <c r="D35" s="9">
-        <v>46254.16999688657</v>
+        <v>46255.66328059028</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>77</v>
@@ -3541,7 +3553,7 @@
         <v>123</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>128</v>
@@ -3559,9 +3571,11 @@
       <c r="B36" s="5">
         <v>46237.580208009254</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46255.663358391204</v>
+      </c>
       <c r="D36" s="5">
-        <v>46240.824531493054</v>
+        <v>46255.66335965278</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>130</v>
@@ -3612,9 +3626,11 @@
       <c r="B37" s="9">
         <v>46237.58026069445</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="9">
+        <v>46255.66334458333</v>
+      </c>
       <c r="D37" s="9">
-        <v>46240.82452775463</v>
+        <v>46255.66334568287</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>133</v>
@@ -3779,7 +3795,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46252.604395</v>
+        <v>46255.66349910879</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>144</v>
@@ -3829,8 +3845,8 @@
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="11" t="s">
-        <v>66</v>
+      <c r="U40" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -5341,7 +5357,7 @@
         <v>217</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>221</v>
@@ -5434,7 +5450,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46239.61757642361</v>
+        <v>46255.66337329861</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>225</v>
@@ -5484,8 +5500,8 @@
       <c r="T69" s="10">
         <v>0</v>
       </c>
-      <c r="U69" s="11" t="s">
-        <v>66</v>
+      <c r="U69" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5553,10 +5569,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I71" s="9">
         <v>46308</v>
@@ -5616,10 +5632,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I72" s="5">
         <v>46308</v>
@@ -5669,10 +5685,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I73" s="9">
         <v>46308</v>
@@ -5722,10 +5738,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I74" s="5">
         <v>46308</v>
@@ -5775,10 +5791,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I75" s="9">
         <v>46308</v>
@@ -5828,10 +5844,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I76" s="5">
         <v>46315</v>
@@ -5891,10 +5907,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I77" s="9">
         <v>46315</v>
@@ -5944,10 +5960,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I78" s="5">
         <v>46315</v>
@@ -5997,10 +6013,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I79" s="9">
         <v>46315</v>
@@ -6050,10 +6066,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I80" s="5">
         <v>46315</v>
@@ -6103,10 +6119,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I81" s="9">
         <v>46316</v>
@@ -6166,10 +6182,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I82" s="5">
         <v>46316</v>
@@ -6219,10 +6235,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I83" s="9">
         <v>46316</v>
@@ -6272,10 +6288,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I84" s="5">
         <v>46316</v>
@@ -6325,10 +6341,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I85" s="9">
         <v>46316</v>
@@ -6378,10 +6394,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I86" s="5">
         <v>46317</v>
@@ -6441,10 +6457,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I87" s="9">
         <v>46317</v>
@@ -6494,10 +6510,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I88" s="5">
         <v>46317</v>
@@ -6547,10 +6563,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I89" s="9">
         <v>46317</v>
@@ -6600,10 +6616,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I90" s="5">
         <v>46317</v>
@@ -6653,10 +6669,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I91" s="9">
         <v>46318</v>
@@ -6716,10 +6732,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I92" s="5">
         <v>46318</v>
@@ -6769,10 +6785,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I93" s="9">
         <v>46318</v>
@@ -6822,10 +6838,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I94" s="5">
         <v>46318</v>
@@ -6875,10 +6891,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I95" s="9">
         <v>46323</v>
@@ -6928,10 +6944,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I96" s="5">
         <v>46321</v>
@@ -6991,10 +7007,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I97" s="9">
         <v>46321</v>
@@ -7044,10 +7060,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I98" s="5">
         <v>46321</v>
@@ -7097,10 +7113,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I99" s="9">
         <v>46321</v>
@@ -7150,10 +7166,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I100" s="5">
         <v>46321</v>
@@ -7203,10 +7219,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I101" s="9">
         <v>46323</v>
@@ -7266,10 +7282,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I102" s="5">
         <v>46323</v>
@@ -7319,10 +7335,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I103" s="9">
         <v>46323</v>
@@ -7372,10 +7388,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I104" s="5">
         <v>46323</v>
@@ -7425,10 +7441,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I105" s="9">
         <v>46323</v>
@@ -7800,10 +7816,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I112" s="5">
         <v>46325</v>
@@ -7863,10 +7879,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I113" s="9">
         <v>46325</v>
@@ -7916,10 +7932,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I114" s="5">
         <v>46325</v>
@@ -7969,10 +7985,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I115" s="9">
         <v>46325</v>
@@ -8022,10 +8038,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -231,61 +231,61 @@
     <t>Baja</t>
   </si>
   <si>
+    <t>1217119120468560</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma   OT 4394</t>
+  </si>
+  <si>
+    <t>Generacion OC Corte plasma OT  4394</t>
+  </si>
+  <si>
+    <t>1217119120468573</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa   OT 4394</t>
+  </si>
+  <si>
+    <t>Preparacion materiales  OT 4394,Generacion Oc 4394</t>
+  </si>
+  <si>
+    <t>1217119015630774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Mecanizado  OT 4394  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC mecanizado  OT 4394 </t>
+  </si>
+  <si>
+    <t>1217117339188565</t>
+  </si>
+  <si>
+    <t>Generación OC Motor OT 4394</t>
+  </si>
+  <si>
+    <t>1217117339188557</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Corte Laser   OT 4394</t>
+  </si>
+  <si>
+    <t>1217119015630789</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion corte laser  ot 4394 ,Generación OC corte laser   ot 4394</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1217119120468560</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma   OT 4394</t>
-  </si>
-  <si>
-    <t>Generacion OC Corte plasma OT  4394</t>
-  </si>
-  <si>
-    <t>1217119120468573</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa   OT 4394</t>
-  </si>
-  <si>
-    <t>Preparacion materiales  OT 4394,Generacion Oc 4394</t>
-  </si>
-  <si>
-    <t>1217119015630774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Mecanizado  OT 4394  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC mecanizado  OT 4394 </t>
-  </si>
-  <si>
-    <t>1217117339188565</t>
-  </si>
-  <si>
-    <t>Generación OC Motor OT 4394</t>
-  </si>
-  <si>
-    <t>1217117339188557</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Corte Laser   OT 4394</t>
-  </si>
-  <si>
-    <t>1217119015630789</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion corte laser  ot 4394 ,Generación OC corte laser   ot 4394</t>
   </si>
   <si>
     <t>1217119129799398</t>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46239.569350798614</v>
+        <v>46255.715312071756</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>61</v>
@@ -2400,23 +2400,23 @@
       <c r="T15" s="10">
         <v>0</v>
       </c>
-      <c r="U15" s="11" t="s">
-        <v>66</v>
+      <c r="U15" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="5">
         <v>46237.570353981486</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46239.56934689815</v>
+        <v>46255.71531288195</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2449,7 +2449,7 @@
         <v>63</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q16" s="5">
         <v>46275</v>
@@ -2463,23 +2463,23 @@
       <c r="T16" s="6">
         <v>0</v>
       </c>
-      <c r="U16" s="11" t="s">
-        <v>66</v>
+      <c r="U16" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="9">
         <v>46237.570357986115</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46239.5693430324</v>
+        <v>46255.71531201389</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2512,7 +2512,7 @@
         <v>63</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q17" s="9">
         <v>46275</v>
@@ -2526,23 +2526,23 @@
       <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="11" t="s">
-        <v>66</v>
+      <c r="U17" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5">
         <v>46237.57036226852</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46239.56933935185</v>
+        <v>46255.715312361106</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2575,7 +2575,7 @@
         <v>63</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="5">
         <v>46275</v>
@@ -2589,13 +2589,13 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="11" t="s">
-        <v>66</v>
+      <c r="U18" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" s="9">
         <v>46237.579729386576</v>
@@ -2640,7 +2640,7 @@
         <v>43</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="9">
         <v>46245</v>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20" s="5">
         <v>46237.570187731486</v>
@@ -2670,7 +2670,7 @@
         <v>46237.79138571759</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2694,7 +2694,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2707,7 +2707,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="9">
         <v>46237.57036725694</v>
@@ -2717,16 +2717,16 @@
         <v>46239.56948452546</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="I21" s="9">
         <v>46276</v>
@@ -2744,13 +2744,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q21" s="9">
         <v>46290</v>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -2786,10 +2786,10 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="I22" s="5">
         <v>46276</v>
@@ -2807,7 +2807,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>61</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2845,10 +2845,10 @@
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="I23" s="9">
         <v>46281</v>
@@ -2866,7 +2866,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>86</v>
@@ -2883,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -2904,10 +2904,10 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="I24" s="5">
         <v>46276</v>
@@ -2925,7 +2925,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>93</v>
@@ -2946,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -2961,16 +2961,16 @@
         <v>46239.56972798611</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="I25" s="9">
         <v>46276</v>
@@ -2991,7 +2991,7 @@
         <v>92</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>95</v>
@@ -3020,10 +3020,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="I26" s="5">
         <v>46281</v>
@@ -3044,7 +3044,7 @@
         <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>98</v>
@@ -3073,10 +3073,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="I27" s="9">
         <v>46276</v>
@@ -3094,7 +3094,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>101</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3130,16 +3130,16 @@
         <v>46239.56982333334</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="I28" s="5">
         <v>46276</v>
@@ -3160,7 +3160,7 @@
         <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>103</v>
@@ -3189,10 +3189,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="I29" s="9">
         <v>46281</v>
@@ -3213,7 +3213,7 @@
         <v>100</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>106</v>
@@ -3263,7 +3263,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>111</v>
@@ -3284,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3329,7 +3329,7 @@
         <v>108</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>114</v>
@@ -3485,7 +3485,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>126</v>
@@ -3523,7 +3523,7 @@
         <v>46255.66328059028</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3608,7 +3608,7 @@
         <v>123</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>131</v>
@@ -3663,7 +3663,7 @@
         <v>123</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>134</v>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46252.60439458334</v>
+        <v>46255.71529688657</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>136</v>
@@ -3793,9 +3793,11 @@
       <c r="B40" s="5">
         <v>46237.57046512731</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46255.71516604167</v>
+      </c>
       <c r="D40" s="5">
-        <v>46255.66349910879</v>
+        <v>46255.715192986114</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>144</v>
@@ -3843,10 +3845,10 @@
         <v>65</v>
       </c>
       <c r="T40" s="6">
-        <v>0</v>
-      </c>
-      <c r="U40" s="12" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U40" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -3856,9 +3858,11 @@
       <c r="B41" s="9">
         <v>46237.57046940972</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="9">
+        <v>46255.71528109953</v>
+      </c>
       <c r="D41" s="9">
-        <v>46239.57030957176</v>
+        <v>46255.71529815972</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>63</v>
@@ -3906,10 +3910,10 @@
         <v>65</v>
       </c>
       <c r="T41" s="10">
-        <v>0</v>
-      </c>
-      <c r="U41" s="11" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U41" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -3972,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4294,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4357,7 +4361,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4420,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4483,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4546,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4609,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4701,7 +4705,7 @@
         <v>187</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>193</v>
@@ -4719,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4782,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4794,7 +4798,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46239.57090008102</v>
+        <v>46255.71530028935</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>157</v>
@@ -4847,7 +4851,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46239.570895972225</v>
+        <v>46255.7152974537</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>157</v>
@@ -4900,7 +4904,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46239.570892222226</v>
+        <v>46255.715298125</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>157</v>
@@ -5055,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5067,7 +5071,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46239.57100972222</v>
+        <v>46255.71530109954</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>157</v>
@@ -5120,7 +5124,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46239.57100552083</v>
+        <v>46255.715298634255</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>157</v>
@@ -5173,7 +5177,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46239.57100167824</v>
+        <v>46255.71529912037</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>157</v>
@@ -5375,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5438,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5611,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5886,7 +5890,7 @@
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6161,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6173,7 +6177,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46239.61779259259</v>
+        <v>46255.71529939814</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>157</v>
@@ -6226,7 +6230,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46239.617791365745</v>
+        <v>46255.7152997338</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>157</v>
@@ -6436,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="U86" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6711,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6986,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7261,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7583,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -7858,7 +7862,7 @@
         <v>0</v>
       </c>
       <c r="U112" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8131,7 +8135,7 @@
         <v>0</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -8406,7 +8410,7 @@
         <v>0</v>
       </c>
       <c r="U122" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
@@ -8728,7 +8732,7 @@
         <v>0</v>
       </c>
       <c r="U128" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
@@ -8791,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="347">
   <si>
     <t>50001591 - "ZITRON COLOMBIA  ARIS MARAMTO"</t>
   </si>
@@ -472,6 +472,9 @@
   </si>
   <si>
     <t>Check Planos  OT 4394,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1217119228070436</t>
@@ -3797,7 +3800,7 @@
         <v>46255.71516604167</v>
       </c>
       <c r="D40" s="5">
-        <v>46255.715192986114</v>
+        <v>46265.18855003473</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>144</v>
@@ -3841,8 +3844,8 @@
       <c r="R40" s="5">
         <v>46266</v>
       </c>
-      <c r="S40" s="7" t="s">
-        <v>65</v>
+      <c r="S40" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -3853,7 +3856,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B41" s="9">
         <v>46237.57046940972</v>
@@ -3871,10 +3874,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" s="9">
         <v>46273</v>
@@ -3898,7 +3901,7 @@
         <v>144</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="9">
         <v>46273</v>
@@ -3918,7 +3921,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46237.570483483796</v>
@@ -3928,16 +3931,16 @@
         <v>46239.60363896991</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I42" s="5">
         <v>46322</v>
@@ -3958,7 +3961,7 @@
         <v>136</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>136</v>
@@ -3981,7 +3984,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="9">
         <v>46237.57048821759</v>
@@ -3991,16 +3994,16 @@
         <v>46239.63445903936</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I43" s="9">
         <v>46322</v>
@@ -4018,13 +4021,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4034,7 +4037,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46237.57049291667</v>
@@ -4044,16 +4047,16 @@
         <v>46239.63445802083</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I44" s="5">
         <v>46322</v>
@@ -4071,13 +4074,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4087,7 +4090,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" s="9">
         <v>46237.57051701389</v>
@@ -4097,16 +4100,16 @@
         <v>46239.63445679398</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I45" s="9">
         <v>46322</v>
@@ -4124,13 +4127,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4140,7 +4143,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46239.60363707176</v>
@@ -4150,16 +4153,16 @@
         <v>46239.65046148148</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I46" s="5">
         <v>46322</v>
@@ -4177,13 +4180,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4193,7 +4196,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B47" s="9">
         <v>46237.57052454861</v>
@@ -4203,7 +4206,7 @@
         <v>46237.796667546296</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>25</v>
@@ -4227,7 +4230,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4240,7 +4243,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B48" s="5">
         <v>46237.57052836806</v>
@@ -4250,16 +4253,16 @@
         <v>46239.57054138889</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I48" s="5">
         <v>46293</v>
@@ -4277,13 +4280,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="5">
         <v>46293</v>
@@ -4303,7 +4306,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" s="9">
         <v>46237.57053329861</v>
@@ -4313,16 +4316,16 @@
         <v>46239.570537754626</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I49" s="9">
         <v>46293</v>
@@ -4340,13 +4343,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>97</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q49" s="9">
         <v>46293</v>
@@ -4366,7 +4369,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46237.57053827547</v>
@@ -4376,16 +4379,16 @@
         <v>46239.570533715276</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I50" s="5">
         <v>46293</v>
@@ -4403,13 +4406,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="5">
         <v>46293</v>
@@ -4429,7 +4432,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="9">
         <v>46237.57054359953</v>
@@ -4439,7 +4442,7 @@
         <v>46239.570621273146</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4466,13 +4469,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q51" s="9">
         <v>46294</v>
@@ -4492,7 +4495,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46237.570548668984</v>
@@ -4502,7 +4505,7 @@
         <v>46239.57061776621</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4529,13 +4532,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q52" s="5">
         <v>46294</v>
@@ -4555,7 +4558,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B53" s="9">
         <v>46237.57055390046</v>
@@ -4565,7 +4568,7 @@
         <v>46239.57061447916</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4592,13 +4595,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="9">
         <v>46294</v>
@@ -4618,7 +4621,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46237.57055873843</v>
@@ -4628,7 +4631,7 @@
         <v>46237.79991431713</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4652,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4665,7 +4668,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B55" s="9">
         <v>46237.570562442124</v>
@@ -4675,16 +4678,16 @@
         <v>46239.608869386575</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I55" s="9">
         <v>46295</v>
@@ -4702,13 +4705,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>70</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q55" s="9">
         <v>46297</v>
@@ -4728,7 +4731,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46237.57056796296</v>
@@ -4738,16 +4741,16 @@
         <v>46239.603713460645</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I56" s="5">
         <v>46300</v>
@@ -4765,13 +4768,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q56" s="5">
         <v>46304</v>
@@ -4791,7 +4794,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B57" s="9">
         <v>46237.57057246528</v>
@@ -4801,16 +4804,16 @@
         <v>46255.71530028935</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I57" s="9">
         <v>46300</v>
@@ -4828,13 +4831,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4844,7 +4847,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46237.570579224535</v>
@@ -4854,16 +4857,16 @@
         <v>46255.7152974537</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I58" s="5">
         <v>46300</v>
@@ -4881,13 +4884,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4897,7 +4900,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B59" s="9">
         <v>46237.570585995374</v>
@@ -4907,16 +4910,16 @@
         <v>46255.715298125</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I59" s="9">
         <v>46300</v>
@@ -4934,13 +4937,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4950,7 +4953,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B60" s="5">
         <v>46239.60371085648</v>
@@ -4960,16 +4963,16 @@
         <v>46239.716654814816</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I60" s="5">
         <v>46300</v>
@@ -4987,13 +4990,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5003,7 +5006,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B61" s="9">
         <v>46237.57064327547</v>
@@ -5013,7 +5016,7 @@
         <v>46239.60380005787</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5038,13 +5041,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q61" s="9">
         <v>46307</v>
@@ -5064,7 +5067,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B62" s="5">
         <v>46237.570648796296</v>
@@ -5074,7 +5077,7 @@
         <v>46255.71530109954</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5101,13 +5104,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5117,7 +5120,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B63" s="9">
         <v>46237.57065361111</v>
@@ -5127,7 +5130,7 @@
         <v>46255.715298634255</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5154,13 +5157,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5170,7 +5173,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B64" s="5">
         <v>46237.57065883101</v>
@@ -5180,7 +5183,7 @@
         <v>46255.71529912037</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5207,13 +5210,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5223,7 +5226,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B65" s="9">
         <v>46239.60379768518</v>
@@ -5233,7 +5236,7 @@
         <v>46239.6206874537</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5258,13 +5261,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5274,7 +5277,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B66" s="5">
         <v>46237.57067465278</v>
@@ -5284,7 +5287,7 @@
         <v>46237.80043872685</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5308,7 +5311,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5321,7 +5324,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B67" s="9">
         <v>46237.570677881944</v>
@@ -5331,16 +5334,16 @@
         <v>46242.17283251157</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I67" s="9">
         <v>46240</v>
@@ -5358,13 +5361,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>51</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q67" s="9">
         <v>46241</v>
@@ -5384,7 +5387,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B68" s="5">
         <v>46237.57068269676</v>
@@ -5394,16 +5397,16 @@
         <v>46242.172833854165</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I68" s="5">
         <v>46240</v>
@@ -5421,13 +5424,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>57</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q68" s="5">
         <v>46241</v>
@@ -5447,7 +5450,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B69" s="9">
         <v>46237.5706884838</v>
@@ -5457,16 +5460,16 @@
         <v>46255.66337329861</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I69" s="9">
         <v>46287</v>
@@ -5484,13 +5487,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>130</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q69" s="9">
         <v>46287</v>
@@ -5510,7 +5513,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B70" s="5">
         <v>46237.570694027774</v>
@@ -5520,7 +5523,7 @@
         <v>46237.808683634255</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5544,7 +5547,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5557,7 +5560,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B71" s="9">
         <v>46237.57069988426</v>
@@ -5567,7 +5570,7 @@
         <v>46239.61845846065</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5594,13 +5597,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q71" s="9">
         <v>46314</v>
@@ -5620,7 +5623,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B72" s="5">
         <v>46237.57070458333</v>
@@ -5630,7 +5633,7 @@
         <v>46239.57127634259</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5657,13 +5660,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5673,7 +5676,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B73" s="9">
         <v>46237.57070806713</v>
@@ -5683,7 +5686,7 @@
         <v>46239.57127222222</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5710,13 +5713,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5726,7 +5729,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B74" s="5">
         <v>46237.57071152778</v>
@@ -5736,7 +5739,7 @@
         <v>46239.57126841435</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5763,13 +5766,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5779,7 +5782,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B75" s="9">
         <v>46239.61845638889</v>
@@ -5789,7 +5792,7 @@
         <v>46239.620747719906</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5816,10 +5819,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -5832,7 +5835,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B76" s="5">
         <v>46237.5792246412</v>
@@ -5842,7 +5845,7 @@
         <v>46239.6097567824</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5869,10 +5872,10 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5895,7 +5898,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B77" s="9">
         <v>46237.60174226852</v>
@@ -5905,7 +5908,7 @@
         <v>46239.571369108795</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5932,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5948,7 +5951,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B78" s="5">
         <v>46237.601752048606</v>
@@ -5958,7 +5961,7 @@
         <v>46239.57136590278</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5985,13 +5988,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6001,7 +6004,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B79" s="9">
         <v>46237.60176081018</v>
@@ -6011,7 +6014,7 @@
         <v>46239.571362627314</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6038,13 +6041,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6054,7 +6057,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B80" s="5">
         <v>46239.60975478009</v>
@@ -6064,7 +6067,7 @@
         <v>46239.64953579861</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6091,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6107,7 +6110,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B81" s="9">
         <v>46237.57076179398</v>
@@ -6117,7 +6120,7 @@
         <v>46239.60978591435</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6144,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q81" s="9">
         <v>46316</v>
@@ -6170,7 +6173,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46237.570767337966</v>
@@ -6180,7 +6183,7 @@
         <v>46255.71529939814</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6207,13 +6210,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6223,7 +6226,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B83" s="9">
         <v>46237.57077200232</v>
@@ -6233,7 +6236,7 @@
         <v>46255.7152997338</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6260,13 +6263,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6276,7 +6279,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B84" s="5">
         <v>46237.570776238426</v>
@@ -6286,7 +6289,7 @@
         <v>46239.61779011574</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6313,13 +6316,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6329,7 +6332,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B85" s="9">
         <v>46239.609783865744</v>
@@ -6339,7 +6342,7 @@
         <v>46239.617714872686</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6366,10 +6369,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6382,7 +6385,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B86" s="5">
         <v>46237.570741250005</v>
@@ -6392,7 +6395,7 @@
         <v>46239.60983028935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6419,13 +6422,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q86" s="5">
         <v>46317</v>
@@ -6445,7 +6448,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B87" s="9">
         <v>46237.57074578704</v>
@@ -6455,7 +6458,7 @@
         <v>46239.57192630787</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6482,13 +6485,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6498,7 +6501,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B88" s="5">
         <v>46237.57074978009</v>
@@ -6508,7 +6511,7 @@
         <v>46239.57192538194</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6535,13 +6538,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6551,7 +6554,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B89" s="9">
         <v>46237.570753935186</v>
@@ -6561,7 +6564,7 @@
         <v>46239.57192444445</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6588,13 +6591,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6604,7 +6607,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B90" s="5">
         <v>46239.6098277662</v>
@@ -6614,7 +6617,7 @@
         <v>46239.62314922454</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6641,10 +6644,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6657,7 +6660,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B91" s="9">
         <v>46237.57069734954</v>
@@ -6667,7 +6670,7 @@
         <v>46239.60986582176</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6694,13 +6697,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q91" s="9">
         <v>46318</v>
@@ -6720,7 +6723,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B92" s="5">
         <v>46237.60193265046</v>
@@ -6730,7 +6733,7 @@
         <v>46239.60990070602</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6757,13 +6760,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6773,7 +6776,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B93" s="9">
         <v>46237.601940740744</v>
@@ -6783,7 +6786,7 @@
         <v>46239.6099468287</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6810,13 +6813,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6826,7 +6829,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B94" s="5">
         <v>46237.60194800926</v>
@@ -6836,7 +6839,7 @@
         <v>46239.60997769676</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6863,13 +6866,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6879,7 +6882,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B95" s="9">
         <v>46239.609863680555</v>
@@ -6889,7 +6892,7 @@
         <v>46239.63397174768</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6916,10 +6919,10 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>26</v>
@@ -6932,7 +6935,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B96" s="5">
         <v>46237.570830474535</v>
@@ -6942,7 +6945,7 @@
         <v>46239.61000172453</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6969,13 +6972,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q96" s="5">
         <v>46321</v>
@@ -6995,7 +6998,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B97" s="9">
         <v>46237.57083550926</v>
@@ -7005,7 +7008,7 @@
         <v>46239.572179930554</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7032,13 +7035,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7048,7 +7051,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B98" s="5">
         <v>46237.570847511575</v>
@@ -7058,7 +7061,7 @@
         <v>46239.57217587963</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7085,13 +7088,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7101,7 +7104,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B99" s="9">
         <v>46237.570855555554</v>
@@ -7111,7 +7114,7 @@
         <v>46239.57217159722</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7138,13 +7141,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7154,7 +7157,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B100" s="5">
         <v>46239.609999629625</v>
@@ -7164,7 +7167,7 @@
         <v>46239.634635740746</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7191,13 +7194,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7207,7 +7210,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B101" s="9">
         <v>46237.57086628472</v>
@@ -7217,7 +7220,7 @@
         <v>46239.610039652776</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7244,10 +7247,10 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>26</v>
@@ -7270,7 +7273,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B102" s="5">
         <v>46237.57087083333</v>
@@ -7280,7 +7283,7 @@
         <v>46239.63361798611</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7307,13 +7310,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7323,7 +7326,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B103" s="9">
         <v>46237.57087578704</v>
@@ -7333,7 +7336,7 @@
         <v>46239.63361701389</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7360,13 +7363,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7376,7 +7379,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B104" s="5">
         <v>46237.57088047454</v>
@@ -7386,7 +7389,7 @@
         <v>46239.63367186343</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7413,13 +7416,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7429,7 +7432,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B105" s="9">
         <v>46239.610037488426</v>
@@ -7439,7 +7442,7 @@
         <v>46239.65005603009</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7466,13 +7469,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7482,7 +7485,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B106" s="5">
         <v>46237.57088893518</v>
@@ -7492,7 +7495,7 @@
         <v>46237.81145841435</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>25</v>
@@ -7516,7 +7519,7 @@
         <v>26</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>26</v>
@@ -7529,7 +7532,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B107" s="9">
         <v>46237.570892731484</v>
@@ -7539,16 +7542,16 @@
         <v>46239.605107766205</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I107" s="9">
         <v>46324</v>
@@ -7566,13 +7569,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q107" s="9">
         <v>46324</v>
@@ -7592,7 +7595,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B108" s="5">
         <v>46237.57089802083</v>
@@ -7602,16 +7605,16 @@
         <v>46239.57251351852</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I108" s="5">
         <v>46324</v>
@@ -7629,13 +7632,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7645,7 +7648,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B109" s="9">
         <v>46237.570901921295</v>
@@ -7655,16 +7658,16 @@
         <v>46239.57250958333</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I109" s="9">
         <v>46324</v>
@@ -7682,13 +7685,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7698,7 +7701,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B110" s="5">
         <v>46237.570906064815</v>
@@ -7708,16 +7711,16 @@
         <v>46239.57250601852</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I110" s="5">
         <v>46324</v>
@@ -7735,13 +7738,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7751,7 +7754,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B111" s="9">
         <v>46239.605104699076</v>
@@ -7761,16 +7764,16 @@
         <v>46239.65079266204</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I111" s="9">
         <v>46324</v>
@@ -7788,13 +7791,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7804,7 +7807,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B112" s="5">
         <v>46237.57091384259</v>
@@ -7814,7 +7817,7 @@
         <v>46239.60514053241</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7841,10 +7844,10 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>26</v>
@@ -7867,7 +7870,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B113" s="9">
         <v>46237.570918125</v>
@@ -7877,7 +7880,7 @@
         <v>46239.57274636574</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -7904,13 +7907,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7920,7 +7923,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B114" s="5">
         <v>46237.5709225</v>
@@ -7930,7 +7933,7 @@
         <v>46239.57274300926</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7957,13 +7960,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -7973,7 +7976,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B115" s="9">
         <v>46237.57092643519</v>
@@ -7983,7 +7986,7 @@
         <v>46239.57273921296</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8010,13 +8013,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8026,7 +8029,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B116" s="5">
         <v>46239.60513822916</v>
@@ -8036,7 +8039,7 @@
         <v>46239.65121751158</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8061,13 +8064,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8077,7 +8080,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B117" s="9">
         <v>46237.5709340162</v>
@@ -8087,16 +8090,16 @@
         <v>46239.60517148148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I117" s="9">
         <v>46328</v>
@@ -8114,13 +8117,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q117" s="9">
         <v>46328</v>
@@ -8140,7 +8143,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B118" s="5">
         <v>46237.57093827546</v>
@@ -8150,16 +8153,16 @@
         <v>46239.57292194445</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I118" s="5">
         <v>46328</v>
@@ -8177,13 +8180,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8193,7 +8196,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B119" s="9">
         <v>46237.570942280094</v>
@@ -8203,16 +8206,16 @@
         <v>46239.57291828704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I119" s="9">
         <v>46328</v>
@@ -8230,13 +8233,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8246,7 +8249,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B120" s="5">
         <v>46237.570946203705</v>
@@ -8256,16 +8259,16 @@
         <v>46239.572914687495</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I120" s="5">
         <v>46328</v>
@@ -8283,13 +8286,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8299,7 +8302,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B121" s="9">
         <v>46239.60516900463</v>
@@ -8309,16 +8312,16 @@
         <v>46239.65163626157</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I121" s="9">
         <v>46328</v>
@@ -8336,13 +8339,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8352,7 +8355,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B122" s="5">
         <v>46237.57099806713</v>
@@ -8362,16 +8365,16 @@
         <v>46239.60520445602</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I122" s="5">
         <v>46329</v>
@@ -8389,13 +8392,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q122" s="5">
         <v>46329</v>
@@ -8415,7 +8418,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B123" s="9">
         <v>46237.571004722224</v>
@@ -8425,16 +8428,16 @@
         <v>46239.573137245374</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I123" s="9">
         <v>46329</v>
@@ -8452,13 +8455,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8468,7 +8471,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B124" s="5">
         <v>46237.57100873842</v>
@@ -8478,16 +8481,16 @@
         <v>46239.57312887731</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I124" s="5">
         <v>46329</v>
@@ -8505,13 +8508,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8521,7 +8524,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B125" s="9">
         <v>46237.571012685185</v>
@@ -8531,16 +8534,16 @@
         <v>46239.57312516204</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I125" s="9">
         <v>46329</v>
@@ -8558,13 +8561,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8574,7 +8577,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B126" s="5">
         <v>46239.60520262731</v>
@@ -8584,16 +8587,16 @@
         <v>46239.65181268519</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I126" s="5">
         <v>46329</v>
@@ -8611,10 +8614,10 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -8627,7 +8630,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B127" s="9">
         <v>46237.571019675925</v>
@@ -8637,7 +8640,7 @@
         <v>46237.81196827546</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>25</v>
@@ -8661,7 +8664,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>26</v>
@@ -8674,7 +8677,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B128" s="5">
         <v>46237.571023171295</v>
@@ -8684,16 +8687,16 @@
         <v>46239.57346402778</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I128" s="5">
         <v>46331</v>
@@ -8711,13 +8714,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q128" s="5">
         <v>46339</v>
@@ -8737,7 +8740,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B129" s="9">
         <v>46237.57102857639</v>
@@ -8747,16 +8750,16 @@
         <v>46239.573531319445</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I129" s="9">
         <v>46331</v>
@@ -8774,13 +8777,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q129" s="9">
         <v>46339</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -3865,7 +3865,7 @@
         <v>46255.71528109953</v>
       </c>
       <c r="D41" s="9">
-        <v>46255.71529815972</v>
+        <v>46266.189102731485</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>63</v>
@@ -3909,8 +3909,8 @@
       <c r="R41" s="9">
         <v>46273</v>
       </c>
-      <c r="S41" s="7" t="s">
-        <v>65</v>
+      <c r="S41" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="T41" s="10">
         <v>1</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -228,63 +228,66 @@
     <t>Propuesta compras:,Generación OC corte laser   ot 4394</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1217119120468560</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma   OT 4394</t>
+  </si>
+  <si>
+    <t>Generacion OC Corte plasma OT  4394</t>
+  </si>
+  <si>
+    <t>1217119120468573</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa   OT 4394</t>
+  </si>
+  <si>
+    <t>Preparacion materiales  OT 4394,Generacion Oc 4394</t>
+  </si>
+  <si>
+    <t>1217119015630774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Mecanizado  OT 4394  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC mecanizado  OT 4394 </t>
+  </si>
+  <si>
+    <t>1217117339188565</t>
+  </si>
+  <si>
+    <t>Generación OC Motor OT 4394</t>
+  </si>
+  <si>
+    <t>1217117339188557</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Corte Laser   OT 4394</t>
+  </si>
+  <si>
+    <t>1217119015630789</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion corte laser  ot 4394 ,Generación OC corte laser   ot 4394</t>
+  </si>
+  <si>
     <t>Baja</t>
   </si>
   <si>
-    <t>1217119120468560</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma   OT 4394</t>
-  </si>
-  <si>
-    <t>Generacion OC Corte plasma OT  4394</t>
-  </si>
-  <si>
-    <t>1217119120468573</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa   OT 4394</t>
-  </si>
-  <si>
-    <t>Preparacion materiales  OT 4394,Generacion Oc 4394</t>
-  </si>
-  <si>
-    <t>1217119015630774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Mecanizado  OT 4394  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC mecanizado  OT 4394 </t>
-  </si>
-  <si>
-    <t>1217117339188565</t>
-  </si>
-  <si>
-    <t>Generación OC Motor OT 4394</t>
-  </si>
-  <si>
-    <t>1217117339188557</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Corte Laser   OT 4394</t>
-  </si>
-  <si>
-    <t>1217119015630789</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion corte laser  ot 4394 ,Generación OC corte laser   ot 4394</t>
-  </si>
-  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
@@ -472,9 +475,6 @@
   </si>
   <si>
     <t>Check Planos  OT 4394,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1217119228070436</t>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46255.715312071756</v>
+        <v>46268.17816405093</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>61</v>
@@ -2397,7 +2397,7 @@
       <c r="R15" s="9">
         <v>46274</v>
       </c>
-      <c r="S15" s="7" t="s">
+      <c r="S15" s="12" t="s">
         <v>65</v>
       </c>
       <c r="T15" s="10">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46255.71531288195</v>
+        <v>46268.178164212964</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2460,7 +2460,7 @@
       <c r="R16" s="5">
         <v>46274</v>
       </c>
-      <c r="S16" s="7" t="s">
+      <c r="S16" s="12" t="s">
         <v>65</v>
       </c>
       <c r="T16" s="6">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46255.71531201389</v>
+        <v>46268.1781640625</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>70</v>
@@ -2523,7 +2523,7 @@
       <c r="R17" s="9">
         <v>46274</v>
       </c>
-      <c r="S17" s="7" t="s">
+      <c r="S17" s="12" t="s">
         <v>65</v>
       </c>
       <c r="T17" s="10">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46255.715312361106</v>
+        <v>46268.17816444444</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2586,7 +2586,7 @@
       <c r="R18" s="5">
         <v>46274</v>
       </c>
-      <c r="S18" s="7" t="s">
+      <c r="S18" s="12" t="s">
         <v>65</v>
       </c>
       <c r="T18" s="6">
@@ -2762,18 +2762,18 @@
         <v>46276</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" s="5">
         <v>46237.57037185185</v>
@@ -2783,7 +2783,7 @@
         <v>46239.569636203705</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2816,23 +2816,23 @@
         <v>61</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="9">
         <v>46237.57037601851</v>
@@ -2842,7 +2842,7 @@
         <v>46239.56963283565</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2872,26 +2872,26 @@
         <v>79</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46237.57038045139</v>
@@ -2901,7 +2901,7 @@
         <v>46239.569480694445</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2931,7 +2931,7 @@
         <v>78</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2943,18 +2943,18 @@
         <v>46276</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="9">
         <v>46237.57038452546</v>
@@ -2991,13 +2991,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>67</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46237.57038803241</v>
@@ -3017,7 +3017,7 @@
         <v>46239.569724050925</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3044,13 +3044,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" s="9">
         <v>46237.57039190972</v>
@@ -3070,7 +3070,7 @@
         <v>46239.56947675926</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3100,7 +3100,7 @@
         <v>78</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3112,18 +3112,18 @@
         <v>46276</v>
       </c>
       <c r="S27" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46237.570396006944</v>
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>73</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" s="9">
         <v>46237.570399432865</v>
@@ -3186,7 +3186,7 @@
         <v>46239.56981936343</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3213,13 +3213,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>74</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3229,7 +3229,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5">
         <v>46237.570402893514</v>
@@ -3239,16 +3239,16 @@
         <v>46239.57001657407</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I30" s="5">
         <v>46276</v>
@@ -3269,7 +3269,7 @@
         <v>78</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3281,18 +3281,18 @@
         <v>46276</v>
       </c>
       <c r="S30" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" s="9">
         <v>46237.57040684028</v>
@@ -3302,16 +3302,16 @@
         <v>46239.56992734954</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I31" s="9">
         <v>46276</v>
@@ -3329,13 +3329,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>70</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46237.570411030094</v>
@@ -3355,16 +3355,16 @@
         <v>46239.56992358796</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I32" s="5">
         <v>46289</v>
@@ -3382,13 +3382,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B33" s="9">
         <v>46237.570414699076</v>
@@ -3408,16 +3408,16 @@
         <v>46239.57014509259</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" s="9">
@@ -3433,13 +3433,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46237.580047511576</v>
@@ -3461,16 +3461,16 @@
         <v>46255.66338287037</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I34" s="5">
         <v>46246</v>
@@ -3491,7 +3491,7 @@
         <v>78</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3503,7 +3503,7 @@
         <v>46246</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T34" s="6">
         <v>1</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="9">
         <v>46237.58011546296</v>
@@ -3532,10 +3532,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I35" s="9">
         <v>46246</v>
@@ -3553,13 +3553,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>44</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46237.580208009254</v>
@@ -3581,16 +3581,16 @@
         <v>46255.66335965278</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I36" s="5">
         <v>46255</v>
@@ -3608,13 +3608,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3624,7 +3624,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" s="9">
         <v>46237.58026069445</v>
@@ -3636,16 +3636,16 @@
         <v>46255.66334568287</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I37" s="9">
         <v>46255</v>
@@ -3663,13 +3663,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>76</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3679,7 +3679,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" s="5">
         <v>46237.570455486115</v>
@@ -3689,7 +3689,7 @@
         <v>46255.71529688657</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>25</v>
@@ -3713,7 +3713,7 @@
         <v>26</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" s="9">
         <v>46237.57046002315</v>
@@ -3738,16 +3738,16 @@
         <v>46252.60497945602</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I39" s="9">
         <v>46244</v>
@@ -3765,13 +3765,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>41</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q39" s="9">
         <v>46248</v>
@@ -3791,7 +3791,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46237.57046512731</v>
@@ -3803,16 +3803,16 @@
         <v>46265.18855003473</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I40" s="5">
         <v>46266</v>
@@ -3830,13 +3830,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="5">
         <v>46272</v>
@@ -3845,7 +3845,7 @@
         <v>46266</v>
       </c>
       <c r="S40" s="12" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -3895,10 +3895,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>151</v>
@@ -3910,7 +3910,7 @@
         <v>46273</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="T41" s="10">
         <v>1</v>
@@ -3958,13 +3958,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q42" s="5">
         <v>46322</v>
@@ -3973,13 +3973,13 @@
         <v>46322</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4283,7 +4283,7 @@
         <v>166</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>172</v>
@@ -4295,13 +4295,13 @@
         <v>46293</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4346,7 +4346,7 @@
         <v>166</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>175</v>
@@ -4358,13 +4358,13 @@
         <v>46293</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4409,7 +4409,7 @@
         <v>166</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>178</v>
@@ -4421,13 +4421,13 @@
         <v>46293</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4448,10 +4448,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I51" s="9">
         <v>46294</v>
@@ -4484,13 +4484,13 @@
         <v>46294</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4511,10 +4511,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I52" s="5">
         <v>46294</v>
@@ -4547,13 +4547,13 @@
         <v>46294</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4574,10 +4574,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I53" s="9">
         <v>46294</v>
@@ -4610,13 +4610,13 @@
         <v>46294</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4720,13 +4720,13 @@
         <v>46295</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4783,13 +4783,13 @@
         <v>46300</v>
       </c>
       <c r="S56" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -5022,10 +5022,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5056,13 +5056,13 @@
         <v>46307</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5083,10 +5083,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I62" s="5">
         <v>46307</v>
@@ -5136,10 +5136,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I63" s="9">
         <v>46307</v>
@@ -5189,10 +5189,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I64" s="5">
         <v>46307</v>
@@ -5242,10 +5242,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="9">
@@ -5382,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5445,7 +5445,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5490,7 +5490,7 @@
         <v>218</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>227</v>
@@ -5502,7 +5502,7 @@
         <v>46287</v>
       </c>
       <c r="S69" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
@@ -5612,13 +5612,13 @@
         <v>46308</v>
       </c>
       <c r="S71" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5887,13 +5887,13 @@
         <v>46315</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6162,13 +6162,13 @@
         <v>46316</v>
       </c>
       <c r="S81" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6437,13 +6437,13 @@
         <v>46317</v>
       </c>
       <c r="S86" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6712,13 +6712,13 @@
         <v>46318</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6987,13 +6987,13 @@
         <v>46321</v>
       </c>
       <c r="S96" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T96" s="6">
         <v>0</v>
       </c>
       <c r="U96" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7262,13 +7262,13 @@
         <v>46323</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7584,13 +7584,13 @@
         <v>46324</v>
       </c>
       <c r="S107" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T107" s="10">
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -7859,13 +7859,13 @@
         <v>46325</v>
       </c>
       <c r="S112" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
       <c r="U112" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8132,13 +8132,13 @@
         <v>46328</v>
       </c>
       <c r="S117" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T117" s="10">
         <v>0</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -8407,13 +8407,13 @@
         <v>46329</v>
       </c>
       <c r="S122" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T122" s="6">
         <v>0</v>
       </c>
       <c r="U122" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
@@ -8729,13 +8729,13 @@
         <v>46331</v>
       </c>
       <c r="S128" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T128" s="6">
         <v>0</v>
       </c>
       <c r="U128" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
@@ -8792,13 +8792,13 @@
         <v>46331</v>
       </c>
       <c r="S129" s="7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T129" s="10">
         <v>0</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -1822,7 +1822,7 @@
         <v>46237.813436516204</v>
       </c>
       <c r="D6" s="5">
-        <v>46239.56901194445</v>
+        <v>46271.57281012731</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1887,7 +1887,7 @@
         <v>46237.81343688657</v>
       </c>
       <c r="D7" s="9">
-        <v>46239.56900780092</v>
+        <v>46271.57281092592</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2070,7 +2070,7 @@
         <v>46252.55308709491</v>
       </c>
       <c r="D10" s="5">
-        <v>46252.553101875004</v>
+        <v>46271.57282909722</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>41</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -3800,7 +3800,7 @@
         <v>46255.71516604167</v>
       </c>
       <c r="D40" s="5">
-        <v>46265.18855003473</v>
+        <v>46273.15732342593</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -3844,8 +3844,8 @@
       <c r="R40" s="5">
         <v>46266</v>
       </c>
-      <c r="S40" s="12" t="s">
-        <v>65</v>
+      <c r="S40" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -3865,7 +3865,7 @@
         <v>46255.71528109953</v>
       </c>
       <c r="D41" s="9">
-        <v>46266.189102731485</v>
+        <v>46274.162274664355</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>63</v>
@@ -3909,8 +3909,8 @@
       <c r="R41" s="9">
         <v>46273</v>
       </c>
-      <c r="S41" s="12" t="s">
-        <v>65</v>
+      <c r="S41" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T41" s="10">
         <v>1</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -2353,7 +2353,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46268.17816405093</v>
+        <v>46275.16888416666</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>61</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46268.178164212964</v>
+        <v>46275.16888564815</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46268.1781640625</v>
+        <v>46275.16888680556</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>70</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46268.17816444444</v>
+        <v>46275.16888189815</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
